--- a/output/version3/test/20-10/MARL/CTDE/RL-RL with CL (+comm)/(RL+RL) test results.xlsx
+++ b/output/version3/test/20-10/MARL/CTDE/RL-RL with CL (+comm)/(RL+RL) test results.xlsx
@@ -471,37 +471,37 @@
         <v>1</v>
       </c>
       <c r="B2" t="n">
-        <v>1049</v>
+        <v>887</v>
       </c>
       <c r="C2" t="n">
-        <v>1220</v>
+        <v>1141</v>
       </c>
       <c r="D2" t="n">
-        <v>1024</v>
+        <v>978</v>
       </c>
       <c r="E2" t="n">
-        <v>918</v>
+        <v>947</v>
       </c>
       <c r="F2" t="n">
-        <v>1075</v>
+        <v>1003</v>
       </c>
       <c r="G2" t="n">
-        <v>967</v>
+        <v>1002</v>
       </c>
       <c r="H2" t="n">
-        <v>988</v>
+        <v>948</v>
       </c>
       <c r="I2" t="n">
-        <v>1051</v>
+        <v>955</v>
       </c>
       <c r="J2" t="n">
-        <v>1034</v>
+        <v>960</v>
       </c>
       <c r="K2" t="n">
-        <v>1021</v>
+        <v>1073</v>
       </c>
       <c r="L2" t="n">
-        <v>1034.7</v>
+        <v>989.4</v>
       </c>
     </row>
     <row r="3">
@@ -509,37 +509,37 @@
         <v>10</v>
       </c>
       <c r="B3" t="n">
-        <v>1015</v>
+        <v>976</v>
       </c>
       <c r="C3" t="n">
-        <v>943</v>
+        <v>1063</v>
       </c>
       <c r="D3" t="n">
-        <v>1309</v>
+        <v>988</v>
       </c>
       <c r="E3" t="n">
-        <v>1030</v>
+        <v>934</v>
       </c>
       <c r="F3" t="n">
-        <v>917</v>
+        <v>946</v>
       </c>
       <c r="G3" t="n">
-        <v>988</v>
+        <v>1027</v>
       </c>
       <c r="H3" t="n">
-        <v>966</v>
+        <v>1075</v>
       </c>
       <c r="I3" t="n">
-        <v>1008</v>
+        <v>918</v>
       </c>
       <c r="J3" t="n">
-        <v>1230</v>
+        <v>1025</v>
       </c>
       <c r="K3" t="n">
-        <v>1187</v>
+        <v>1017</v>
       </c>
       <c r="L3" t="n">
-        <v>1059.3</v>
+        <v>996.9</v>
       </c>
     </row>
     <row r="4">
@@ -547,37 +547,37 @@
         <v>11</v>
       </c>
       <c r="B4" t="n">
-        <v>921</v>
+        <v>838</v>
       </c>
       <c r="C4" t="n">
-        <v>930</v>
+        <v>966</v>
       </c>
       <c r="D4" t="n">
-        <v>1118</v>
+        <v>986</v>
       </c>
       <c r="E4" t="n">
-        <v>1042</v>
+        <v>954</v>
       </c>
       <c r="F4" t="n">
-        <v>959</v>
+        <v>940</v>
       </c>
       <c r="G4" t="n">
-        <v>961</v>
+        <v>1017</v>
       </c>
       <c r="H4" t="n">
-        <v>990</v>
+        <v>875</v>
       </c>
       <c r="I4" t="n">
-        <v>1327</v>
+        <v>920</v>
       </c>
       <c r="J4" t="n">
-        <v>928</v>
+        <v>944</v>
       </c>
       <c r="K4" t="n">
-        <v>1014</v>
+        <v>984</v>
       </c>
       <c r="L4" t="n">
-        <v>1019</v>
+        <v>942.4</v>
       </c>
     </row>
     <row r="5">
@@ -585,37 +585,37 @@
         <v>12</v>
       </c>
       <c r="B5" t="n">
-        <v>1242</v>
+        <v>1021</v>
       </c>
       <c r="C5" t="n">
-        <v>882</v>
+        <v>894</v>
       </c>
       <c r="D5" t="n">
-        <v>886</v>
+        <v>811</v>
       </c>
       <c r="E5" t="n">
-        <v>939</v>
+        <v>960</v>
       </c>
       <c r="F5" t="n">
-        <v>1274</v>
+        <v>804</v>
       </c>
       <c r="G5" t="n">
-        <v>957</v>
+        <v>1071</v>
       </c>
       <c r="H5" t="n">
-        <v>943</v>
+        <v>927</v>
       </c>
       <c r="I5" t="n">
-        <v>1039</v>
+        <v>831</v>
       </c>
       <c r="J5" t="n">
-        <v>904</v>
+        <v>817</v>
       </c>
       <c r="K5" t="n">
-        <v>1211</v>
+        <v>1012</v>
       </c>
       <c r="L5" t="n">
-        <v>1027.7</v>
+        <v>914.8</v>
       </c>
     </row>
     <row r="6">
@@ -623,37 +623,37 @@
         <v>13</v>
       </c>
       <c r="B6" t="n">
-        <v>972</v>
+        <v>1085</v>
       </c>
       <c r="C6" t="n">
-        <v>1063</v>
+        <v>885</v>
       </c>
       <c r="D6" t="n">
+        <v>870</v>
+      </c>
+      <c r="E6" t="n">
+        <v>832</v>
+      </c>
+      <c r="F6" t="n">
+        <v>969</v>
+      </c>
+      <c r="G6" t="n">
+        <v>951</v>
+      </c>
+      <c r="H6" t="n">
+        <v>866</v>
+      </c>
+      <c r="I6" t="n">
+        <v>1095</v>
+      </c>
+      <c r="J6" t="n">
+        <v>953</v>
+      </c>
+      <c r="K6" t="n">
         <v>948</v>
       </c>
-      <c r="E6" t="n">
-        <v>1052</v>
-      </c>
-      <c r="F6" t="n">
-        <v>1135</v>
-      </c>
-      <c r="G6" t="n">
-        <v>1104</v>
-      </c>
-      <c r="H6" t="n">
-        <v>1277</v>
-      </c>
-      <c r="I6" t="n">
-        <v>922</v>
-      </c>
-      <c r="J6" t="n">
-        <v>1254</v>
-      </c>
-      <c r="K6" t="n">
-        <v>1087</v>
-      </c>
       <c r="L6" t="n">
-        <v>1081.4</v>
+        <v>945.4</v>
       </c>
     </row>
     <row r="7">
@@ -661,37 +661,37 @@
         <v>14</v>
       </c>
       <c r="B7" t="n">
-        <v>1091</v>
+        <v>959</v>
       </c>
       <c r="C7" t="n">
-        <v>998</v>
+        <v>1087</v>
       </c>
       <c r="D7" t="n">
-        <v>1010</v>
+        <v>900</v>
       </c>
       <c r="E7" t="n">
-        <v>1038</v>
+        <v>1014</v>
       </c>
       <c r="F7" t="n">
+        <v>928</v>
+      </c>
+      <c r="G7" t="n">
+        <v>1131</v>
+      </c>
+      <c r="H7" t="n">
         <v>933</v>
       </c>
-      <c r="G7" t="n">
-        <v>1218</v>
-      </c>
-      <c r="H7" t="n">
-        <v>1013</v>
-      </c>
       <c r="I7" t="n">
-        <v>1061</v>
+        <v>845</v>
       </c>
       <c r="J7" t="n">
-        <v>927</v>
+        <v>870</v>
       </c>
       <c r="K7" t="n">
-        <v>1040</v>
+        <v>970</v>
       </c>
       <c r="L7" t="n">
-        <v>1032.9</v>
+        <v>963.7</v>
       </c>
     </row>
     <row r="8">
@@ -699,37 +699,37 @@
         <v>15</v>
       </c>
       <c r="B8" t="n">
-        <v>1008</v>
+        <v>980</v>
       </c>
       <c r="C8" t="n">
-        <v>1090</v>
+        <v>1113</v>
       </c>
       <c r="D8" t="n">
-        <v>912</v>
+        <v>937</v>
       </c>
       <c r="E8" t="n">
-        <v>1142</v>
+        <v>943</v>
       </c>
       <c r="F8" t="n">
-        <v>982</v>
+        <v>933</v>
       </c>
       <c r="G8" t="n">
-        <v>1169</v>
+        <v>938</v>
       </c>
       <c r="H8" t="n">
-        <v>986</v>
+        <v>1084</v>
       </c>
       <c r="I8" t="n">
-        <v>1013</v>
+        <v>960</v>
       </c>
       <c r="J8" t="n">
-        <v>1245</v>
+        <v>995</v>
       </c>
       <c r="K8" t="n">
-        <v>1166</v>
+        <v>985</v>
       </c>
       <c r="L8" t="n">
-        <v>1071.3</v>
+        <v>986.8</v>
       </c>
     </row>
     <row r="9">
@@ -737,37 +737,37 @@
         <v>16</v>
       </c>
       <c r="B9" t="n">
-        <v>1165</v>
+        <v>910</v>
       </c>
       <c r="C9" t="n">
-        <v>931</v>
+        <v>972</v>
       </c>
       <c r="D9" t="n">
-        <v>1010</v>
+        <v>1012</v>
       </c>
       <c r="E9" t="n">
-        <v>1045</v>
+        <v>992</v>
       </c>
       <c r="F9" t="n">
-        <v>1075</v>
+        <v>908</v>
       </c>
       <c r="G9" t="n">
-        <v>959</v>
+        <v>914</v>
       </c>
       <c r="H9" t="n">
-        <v>1088</v>
+        <v>870</v>
       </c>
       <c r="I9" t="n">
-        <v>925</v>
+        <v>939</v>
       </c>
       <c r="J9" t="n">
-        <v>1117</v>
+        <v>816</v>
       </c>
       <c r="K9" t="n">
-        <v>1032</v>
+        <v>927</v>
       </c>
       <c r="L9" t="n">
-        <v>1034.7</v>
+        <v>926</v>
       </c>
     </row>
     <row r="10">
@@ -775,37 +775,37 @@
         <v>17</v>
       </c>
       <c r="B10" t="n">
-        <v>919</v>
+        <v>874</v>
       </c>
       <c r="C10" t="n">
-        <v>1044</v>
+        <v>841</v>
       </c>
       <c r="D10" t="n">
-        <v>1016</v>
+        <v>858</v>
       </c>
       <c r="E10" t="n">
-        <v>858</v>
+        <v>883</v>
       </c>
       <c r="F10" t="n">
-        <v>867</v>
+        <v>846</v>
       </c>
       <c r="G10" t="n">
-        <v>1038</v>
+        <v>848</v>
       </c>
       <c r="H10" t="n">
-        <v>839</v>
+        <v>739</v>
       </c>
       <c r="I10" t="n">
-        <v>1025</v>
+        <v>885</v>
       </c>
       <c r="J10" t="n">
-        <v>1092</v>
+        <v>811</v>
       </c>
       <c r="K10" t="n">
-        <v>951</v>
+        <v>863</v>
       </c>
       <c r="L10" t="n">
-        <v>964.9</v>
+        <v>844.8</v>
       </c>
     </row>
     <row r="11">
@@ -813,37 +813,37 @@
         <v>18</v>
       </c>
       <c r="B11" t="n">
-        <v>1032</v>
+        <v>895</v>
       </c>
       <c r="C11" t="n">
-        <v>977</v>
+        <v>855</v>
       </c>
       <c r="D11" t="n">
-        <v>983</v>
+        <v>878</v>
       </c>
       <c r="E11" t="n">
-        <v>990</v>
+        <v>916</v>
       </c>
       <c r="F11" t="n">
         <v>925</v>
       </c>
       <c r="G11" t="n">
-        <v>979</v>
+        <v>898</v>
       </c>
       <c r="H11" t="n">
-        <v>969</v>
+        <v>971</v>
       </c>
       <c r="I11" t="n">
-        <v>1075</v>
+        <v>846</v>
       </c>
       <c r="J11" t="n">
-        <v>965</v>
+        <v>834</v>
       </c>
       <c r="K11" t="n">
-        <v>885</v>
+        <v>976</v>
       </c>
       <c r="L11" t="n">
-        <v>978</v>
+        <v>899.4</v>
       </c>
     </row>
     <row r="12">
@@ -851,37 +851,37 @@
         <v>19</v>
       </c>
       <c r="B12" t="n">
-        <v>932</v>
+        <v>984</v>
       </c>
       <c r="C12" t="n">
-        <v>991</v>
+        <v>855</v>
       </c>
       <c r="D12" t="n">
-        <v>977</v>
+        <v>961</v>
       </c>
       <c r="E12" t="n">
-        <v>1040</v>
+        <v>815</v>
       </c>
       <c r="F12" t="n">
-        <v>981</v>
+        <v>872</v>
       </c>
       <c r="G12" t="n">
-        <v>1017</v>
+        <v>946</v>
       </c>
       <c r="H12" t="n">
-        <v>1054</v>
+        <v>859</v>
       </c>
       <c r="I12" t="n">
-        <v>1067</v>
+        <v>962</v>
       </c>
       <c r="J12" t="n">
-        <v>1362</v>
+        <v>921</v>
       </c>
       <c r="K12" t="n">
-        <v>1243</v>
+        <v>982</v>
       </c>
       <c r="L12" t="n">
-        <v>1066.4</v>
+        <v>915.7</v>
       </c>
     </row>
     <row r="13">
@@ -889,37 +889,37 @@
         <v>2</v>
       </c>
       <c r="B13" t="n">
-        <v>905</v>
+        <v>870</v>
       </c>
       <c r="C13" t="n">
-        <v>912</v>
+        <v>850</v>
       </c>
       <c r="D13" t="n">
-        <v>1046</v>
+        <v>924</v>
       </c>
       <c r="E13" t="n">
-        <v>971</v>
+        <v>914</v>
       </c>
       <c r="F13" t="n">
-        <v>1032</v>
+        <v>844</v>
       </c>
       <c r="G13" t="n">
-        <v>944</v>
+        <v>1018</v>
       </c>
       <c r="H13" t="n">
-        <v>1102</v>
+        <v>848</v>
       </c>
       <c r="I13" t="n">
-        <v>941</v>
+        <v>898</v>
       </c>
       <c r="J13" t="n">
-        <v>932</v>
+        <v>908</v>
       </c>
       <c r="K13" t="n">
-        <v>1255</v>
+        <v>1057</v>
       </c>
       <c r="L13" t="n">
-        <v>1004</v>
+        <v>913.1</v>
       </c>
     </row>
     <row r="14">
@@ -927,37 +927,37 @@
         <v>20</v>
       </c>
       <c r="B14" t="n">
-        <v>1204</v>
+        <v>992</v>
       </c>
       <c r="C14" t="n">
-        <v>1222</v>
+        <v>902</v>
       </c>
       <c r="D14" t="n">
-        <v>1298</v>
+        <v>1006</v>
       </c>
       <c r="E14" t="n">
-        <v>1030</v>
+        <v>1007</v>
       </c>
       <c r="F14" t="n">
-        <v>1228</v>
+        <v>1003</v>
       </c>
       <c r="G14" t="n">
-        <v>1024</v>
+        <v>899</v>
       </c>
       <c r="H14" t="n">
-        <v>1167</v>
+        <v>1000</v>
       </c>
       <c r="I14" t="n">
-        <v>1144</v>
+        <v>885</v>
       </c>
       <c r="J14" t="n">
-        <v>1058</v>
+        <v>972</v>
       </c>
       <c r="K14" t="n">
-        <v>1002</v>
+        <v>1045</v>
       </c>
       <c r="L14" t="n">
-        <v>1137.7</v>
+        <v>971.1</v>
       </c>
     </row>
     <row r="15">
@@ -965,37 +965,37 @@
         <v>21</v>
       </c>
       <c r="B15" t="n">
-        <v>1141</v>
+        <v>979</v>
       </c>
       <c r="C15" t="n">
-        <v>1047</v>
+        <v>922</v>
       </c>
       <c r="D15" t="n">
-        <v>1003</v>
+        <v>898</v>
       </c>
       <c r="E15" t="n">
-        <v>1127</v>
+        <v>1063</v>
       </c>
       <c r="F15" t="n">
-        <v>905</v>
+        <v>875</v>
       </c>
       <c r="G15" t="n">
-        <v>853</v>
+        <v>866</v>
       </c>
       <c r="H15" t="n">
-        <v>1177</v>
+        <v>918</v>
       </c>
       <c r="I15" t="n">
-        <v>1072</v>
+        <v>967</v>
       </c>
       <c r="J15" t="n">
-        <v>1111</v>
+        <v>1030</v>
       </c>
       <c r="K15" t="n">
-        <v>1097</v>
+        <v>935</v>
       </c>
       <c r="L15" t="n">
-        <v>1053.3</v>
+        <v>945.3</v>
       </c>
     </row>
     <row r="16">
@@ -1003,37 +1003,37 @@
         <v>22</v>
       </c>
       <c r="B16" t="n">
-        <v>1070</v>
+        <v>1072</v>
       </c>
       <c r="C16" t="n">
-        <v>1044</v>
+        <v>956</v>
       </c>
       <c r="D16" t="n">
-        <v>1048</v>
+        <v>913</v>
       </c>
       <c r="E16" t="n">
-        <v>1328</v>
+        <v>854</v>
       </c>
       <c r="F16" t="n">
-        <v>1043</v>
+        <v>851</v>
       </c>
       <c r="G16" t="n">
-        <v>974</v>
+        <v>819</v>
       </c>
       <c r="H16" t="n">
-        <v>1011</v>
+        <v>871</v>
       </c>
       <c r="I16" t="n">
-        <v>1032</v>
+        <v>903</v>
       </c>
       <c r="J16" t="n">
-        <v>947</v>
+        <v>917</v>
       </c>
       <c r="K16" t="n">
-        <v>1077</v>
+        <v>1086</v>
       </c>
       <c r="L16" t="n">
-        <v>1057.4</v>
+        <v>924.2</v>
       </c>
     </row>
     <row r="17">
@@ -1041,37 +1041,37 @@
         <v>23</v>
       </c>
       <c r="B17" t="n">
-        <v>898</v>
+        <v>804</v>
       </c>
       <c r="C17" t="n">
-        <v>954</v>
+        <v>848</v>
       </c>
       <c r="D17" t="n">
+        <v>940</v>
+      </c>
+      <c r="E17" t="n">
+        <v>927</v>
+      </c>
+      <c r="F17" t="n">
+        <v>819</v>
+      </c>
+      <c r="G17" t="n">
+        <v>810</v>
+      </c>
+      <c r="H17" t="n">
+        <v>967</v>
+      </c>
+      <c r="I17" t="n">
+        <v>880</v>
+      </c>
+      <c r="J17" t="n">
         <v>973</v>
       </c>
-      <c r="E17" t="n">
-        <v>1077</v>
-      </c>
-      <c r="F17" t="n">
-        <v>1026</v>
-      </c>
-      <c r="G17" t="n">
-        <v>956</v>
-      </c>
-      <c r="H17" t="n">
-        <v>870</v>
-      </c>
-      <c r="I17" t="n">
-        <v>889</v>
-      </c>
-      <c r="J17" t="n">
-        <v>1082</v>
-      </c>
       <c r="K17" t="n">
-        <v>1087</v>
+        <v>913</v>
       </c>
       <c r="L17" t="n">
-        <v>981.2</v>
+        <v>888.1</v>
       </c>
     </row>
     <row r="18">
@@ -1079,37 +1079,37 @@
         <v>24</v>
       </c>
       <c r="B18" t="n">
-        <v>1087</v>
+        <v>1037</v>
       </c>
       <c r="C18" t="n">
-        <v>975</v>
+        <v>1073</v>
       </c>
       <c r="D18" t="n">
-        <v>1097</v>
+        <v>982</v>
       </c>
       <c r="E18" t="n">
-        <v>1065</v>
+        <v>1020</v>
       </c>
       <c r="F18" t="n">
-        <v>1271</v>
+        <v>1115</v>
       </c>
       <c r="G18" t="n">
-        <v>1212</v>
+        <v>982</v>
       </c>
       <c r="H18" t="n">
-        <v>1289</v>
+        <v>891</v>
       </c>
       <c r="I18" t="n">
-        <v>1132</v>
+        <v>1005</v>
       </c>
       <c r="J18" t="n">
-        <v>1138</v>
+        <v>867</v>
       </c>
       <c r="K18" t="n">
-        <v>1051</v>
+        <v>1039</v>
       </c>
       <c r="L18" t="n">
-        <v>1131.7</v>
+        <v>1001.1</v>
       </c>
     </row>
     <row r="19">
@@ -1117,37 +1117,37 @@
         <v>25</v>
       </c>
       <c r="B19" t="n">
-        <v>1013</v>
+        <v>747</v>
       </c>
       <c r="C19" t="n">
-        <v>954</v>
+        <v>826</v>
       </c>
       <c r="D19" t="n">
-        <v>1138</v>
+        <v>875</v>
       </c>
       <c r="E19" t="n">
-        <v>1056</v>
+        <v>739</v>
       </c>
       <c r="F19" t="n">
-        <v>864</v>
+        <v>892</v>
       </c>
       <c r="G19" t="n">
-        <v>871</v>
+        <v>942</v>
       </c>
       <c r="H19" t="n">
-        <v>1080</v>
+        <v>817</v>
       </c>
       <c r="I19" t="n">
-        <v>966</v>
+        <v>922</v>
       </c>
       <c r="J19" t="n">
-        <v>1080</v>
+        <v>910</v>
       </c>
       <c r="K19" t="n">
-        <v>1045</v>
+        <v>934</v>
       </c>
       <c r="L19" t="n">
-        <v>1006.7</v>
+        <v>860.4</v>
       </c>
     </row>
     <row r="20">
@@ -1155,37 +1155,37 @@
         <v>26</v>
       </c>
       <c r="B20" t="n">
-        <v>887</v>
+        <v>939</v>
       </c>
       <c r="C20" t="n">
-        <v>1020</v>
+        <v>774</v>
       </c>
       <c r="D20" t="n">
-        <v>957</v>
+        <v>893</v>
       </c>
       <c r="E20" t="n">
-        <v>988</v>
+        <v>824</v>
       </c>
       <c r="F20" t="n">
-        <v>875</v>
+        <v>733</v>
       </c>
       <c r="G20" t="n">
-        <v>1209</v>
+        <v>919</v>
       </c>
       <c r="H20" t="n">
-        <v>835</v>
+        <v>881</v>
       </c>
       <c r="I20" t="n">
-        <v>1047</v>
+        <v>931</v>
       </c>
       <c r="J20" t="n">
-        <v>976</v>
+        <v>819</v>
       </c>
       <c r="K20" t="n">
-        <v>966</v>
+        <v>907</v>
       </c>
       <c r="L20" t="n">
-        <v>976</v>
+        <v>862</v>
       </c>
     </row>
     <row r="21">
@@ -1193,37 +1193,37 @@
         <v>27</v>
       </c>
       <c r="B21" t="n">
-        <v>1058</v>
+        <v>1002</v>
       </c>
       <c r="C21" t="n">
-        <v>1121</v>
+        <v>865</v>
       </c>
       <c r="D21" t="n">
-        <v>1094</v>
+        <v>923</v>
       </c>
       <c r="E21" t="n">
-        <v>1127</v>
+        <v>1064</v>
       </c>
       <c r="F21" t="n">
-        <v>1007</v>
+        <v>1090</v>
       </c>
       <c r="G21" t="n">
-        <v>1093</v>
+        <v>1026</v>
       </c>
       <c r="H21" t="n">
-        <v>1115</v>
+        <v>953</v>
       </c>
       <c r="I21" t="n">
-        <v>964</v>
+        <v>1155</v>
       </c>
       <c r="J21" t="n">
-        <v>1116</v>
+        <v>1144</v>
       </c>
       <c r="K21" t="n">
-        <v>1261</v>
+        <v>1054</v>
       </c>
       <c r="L21" t="n">
-        <v>1095.6</v>
+        <v>1027.6</v>
       </c>
     </row>
     <row r="22">
@@ -1231,37 +1231,37 @@
         <v>28</v>
       </c>
       <c r="B22" t="n">
-        <v>1016</v>
+        <v>890</v>
       </c>
       <c r="C22" t="n">
-        <v>913</v>
+        <v>1000</v>
       </c>
       <c r="D22" t="n">
-        <v>961</v>
+        <v>773</v>
       </c>
       <c r="E22" t="n">
-        <v>930</v>
+        <v>873</v>
       </c>
       <c r="F22" t="n">
-        <v>1120</v>
+        <v>839</v>
       </c>
       <c r="G22" t="n">
-        <v>870</v>
+        <v>943</v>
       </c>
       <c r="H22" t="n">
-        <v>885</v>
+        <v>921</v>
       </c>
       <c r="I22" t="n">
-        <v>1150</v>
+        <v>864</v>
       </c>
       <c r="J22" t="n">
-        <v>1089</v>
+        <v>967</v>
       </c>
       <c r="K22" t="n">
-        <v>1002</v>
+        <v>867</v>
       </c>
       <c r="L22" t="n">
-        <v>993.6</v>
+        <v>893.7</v>
       </c>
     </row>
     <row r="23">
@@ -1269,37 +1269,37 @@
         <v>29</v>
       </c>
       <c r="B23" t="n">
-        <v>1147</v>
+        <v>946</v>
       </c>
       <c r="C23" t="n">
-        <v>985</v>
+        <v>958</v>
       </c>
       <c r="D23" t="n">
-        <v>1005</v>
+        <v>1014</v>
       </c>
       <c r="E23" t="n">
-        <v>1088</v>
+        <v>1102</v>
       </c>
       <c r="F23" t="n">
-        <v>1050</v>
+        <v>959</v>
       </c>
       <c r="G23" t="n">
-        <v>1102</v>
+        <v>910</v>
       </c>
       <c r="H23" t="n">
-        <v>913</v>
+        <v>1053</v>
       </c>
       <c r="I23" t="n">
-        <v>1073</v>
+        <v>1016</v>
       </c>
       <c r="J23" t="n">
-        <v>997</v>
+        <v>836</v>
       </c>
       <c r="K23" t="n">
-        <v>1156</v>
+        <v>883</v>
       </c>
       <c r="L23" t="n">
-        <v>1051.6</v>
+        <v>967.7</v>
       </c>
     </row>
     <row r="24">
@@ -1307,37 +1307,37 @@
         <v>3</v>
       </c>
       <c r="B24" t="n">
-        <v>908</v>
+        <v>891</v>
       </c>
       <c r="C24" t="n">
-        <v>980</v>
+        <v>843</v>
       </c>
       <c r="D24" t="n">
-        <v>1032</v>
+        <v>816</v>
       </c>
       <c r="E24" t="n">
-        <v>1049</v>
+        <v>895</v>
       </c>
       <c r="F24" t="n">
-        <v>997</v>
+        <v>885</v>
       </c>
       <c r="G24" t="n">
-        <v>1109</v>
+        <v>887</v>
       </c>
       <c r="H24" t="n">
-        <v>1011</v>
+        <v>871</v>
       </c>
       <c r="I24" t="n">
-        <v>1020</v>
+        <v>905</v>
       </c>
       <c r="J24" t="n">
-        <v>1004</v>
+        <v>815</v>
       </c>
       <c r="K24" t="n">
-        <v>923</v>
+        <v>837</v>
       </c>
       <c r="L24" t="n">
-        <v>1003.3</v>
+        <v>864.5</v>
       </c>
     </row>
     <row r="25">
@@ -1345,37 +1345,37 @@
         <v>30</v>
       </c>
       <c r="B25" t="n">
-        <v>1167</v>
+        <v>975</v>
       </c>
       <c r="C25" t="n">
-        <v>1002</v>
+        <v>1022</v>
       </c>
       <c r="D25" t="n">
-        <v>1213</v>
+        <v>936</v>
       </c>
       <c r="E25" t="n">
-        <v>1248</v>
+        <v>1041</v>
       </c>
       <c r="F25" t="n">
-        <v>1007</v>
+        <v>880</v>
       </c>
       <c r="G25" t="n">
-        <v>1268</v>
+        <v>990</v>
       </c>
       <c r="H25" t="n">
-        <v>1081</v>
+        <v>953</v>
       </c>
       <c r="I25" t="n">
-        <v>980</v>
+        <v>1087</v>
       </c>
       <c r="J25" t="n">
-        <v>1005</v>
+        <v>884</v>
       </c>
       <c r="K25" t="n">
-        <v>950</v>
+        <v>906</v>
       </c>
       <c r="L25" t="n">
-        <v>1092.1</v>
+        <v>967.4</v>
       </c>
     </row>
     <row r="26">
@@ -1383,37 +1383,37 @@
         <v>31</v>
       </c>
       <c r="B26" t="n">
-        <v>1132</v>
+        <v>1023</v>
       </c>
       <c r="C26" t="n">
-        <v>1279</v>
+        <v>1111</v>
       </c>
       <c r="D26" t="n">
-        <v>1109</v>
+        <v>971</v>
       </c>
       <c r="E26" t="n">
-        <v>1215</v>
+        <v>869</v>
       </c>
       <c r="F26" t="n">
-        <v>1036</v>
+        <v>958</v>
       </c>
       <c r="G26" t="n">
-        <v>1161</v>
+        <v>1002</v>
       </c>
       <c r="H26" t="n">
-        <v>1159</v>
+        <v>1041</v>
       </c>
       <c r="I26" t="n">
-        <v>995</v>
+        <v>951</v>
       </c>
       <c r="J26" t="n">
-        <v>1119</v>
+        <v>914</v>
       </c>
       <c r="K26" t="n">
-        <v>1095</v>
+        <v>1012</v>
       </c>
       <c r="L26" t="n">
-        <v>1130</v>
+        <v>985.2</v>
       </c>
     </row>
     <row r="27">
@@ -1421,37 +1421,37 @@
         <v>32</v>
       </c>
       <c r="B27" t="n">
-        <v>1122</v>
+        <v>1044</v>
       </c>
       <c r="C27" t="n">
-        <v>1082</v>
+        <v>1015</v>
       </c>
       <c r="D27" t="n">
-        <v>1056</v>
+        <v>1085</v>
       </c>
       <c r="E27" t="n">
-        <v>971</v>
+        <v>1002</v>
       </c>
       <c r="F27" t="n">
-        <v>1168</v>
+        <v>1090</v>
       </c>
       <c r="G27" t="n">
-        <v>1024</v>
+        <v>1023</v>
       </c>
       <c r="H27" t="n">
-        <v>1147</v>
+        <v>1030</v>
       </c>
       <c r="I27" t="n">
-        <v>1042</v>
+        <v>1064</v>
       </c>
       <c r="J27" t="n">
-        <v>1267</v>
+        <v>1071</v>
       </c>
       <c r="K27" t="n">
-        <v>1150</v>
+        <v>988</v>
       </c>
       <c r="L27" t="n">
-        <v>1102.9</v>
+        <v>1041.2</v>
       </c>
     </row>
     <row r="28">
@@ -1459,37 +1459,37 @@
         <v>33</v>
       </c>
       <c r="B28" t="n">
-        <v>953</v>
+        <v>846</v>
       </c>
       <c r="C28" t="n">
-        <v>862</v>
+        <v>876</v>
       </c>
       <c r="D28" t="n">
-        <v>959</v>
+        <v>941</v>
       </c>
       <c r="E28" t="n">
-        <v>1109</v>
+        <v>887</v>
       </c>
       <c r="F28" t="n">
-        <v>1094</v>
+        <v>796</v>
       </c>
       <c r="G28" t="n">
-        <v>1113</v>
+        <v>923</v>
       </c>
       <c r="H28" t="n">
-        <v>964</v>
+        <v>940</v>
       </c>
       <c r="I28" t="n">
-        <v>1205</v>
+        <v>857</v>
       </c>
       <c r="J28" t="n">
-        <v>1105</v>
+        <v>803</v>
       </c>
       <c r="K28" t="n">
-        <v>1008</v>
+        <v>866</v>
       </c>
       <c r="L28" t="n">
-        <v>1037.2</v>
+        <v>873.5</v>
       </c>
     </row>
     <row r="29">
@@ -1497,37 +1497,37 @@
         <v>34</v>
       </c>
       <c r="B29" t="n">
-        <v>849</v>
+        <v>900</v>
       </c>
       <c r="C29" t="n">
-        <v>911</v>
+        <v>968</v>
       </c>
       <c r="D29" t="n">
-        <v>1222</v>
+        <v>1068</v>
       </c>
       <c r="E29" t="n">
-        <v>1075</v>
+        <v>920</v>
       </c>
       <c r="F29" t="n">
-        <v>1184</v>
+        <v>906</v>
       </c>
       <c r="G29" t="n">
-        <v>1040</v>
+        <v>863</v>
       </c>
       <c r="H29" t="n">
-        <v>936</v>
+        <v>853</v>
       </c>
       <c r="I29" t="n">
-        <v>1086</v>
+        <v>994</v>
       </c>
       <c r="J29" t="n">
-        <v>911</v>
+        <v>894</v>
       </c>
       <c r="K29" t="n">
-        <v>1066</v>
+        <v>995</v>
       </c>
       <c r="L29" t="n">
-        <v>1028</v>
+        <v>936.1</v>
       </c>
     </row>
     <row r="30">
@@ -1535,37 +1535,37 @@
         <v>35</v>
       </c>
       <c r="B30" t="n">
-        <v>1000</v>
+        <v>798</v>
       </c>
       <c r="C30" t="n">
-        <v>893</v>
+        <v>968</v>
       </c>
       <c r="D30" t="n">
-        <v>1041</v>
+        <v>849</v>
       </c>
       <c r="E30" t="n">
-        <v>1099</v>
+        <v>879</v>
       </c>
       <c r="F30" t="n">
-        <v>1149</v>
+        <v>981</v>
       </c>
       <c r="G30" t="n">
-        <v>969</v>
+        <v>871</v>
       </c>
       <c r="H30" t="n">
-        <v>909</v>
+        <v>1006</v>
       </c>
       <c r="I30" t="n">
-        <v>993</v>
+        <v>826</v>
       </c>
       <c r="J30" t="n">
-        <v>913</v>
+        <v>956</v>
       </c>
       <c r="K30" t="n">
-        <v>1113</v>
+        <v>846</v>
       </c>
       <c r="L30" t="n">
-        <v>1007.9</v>
+        <v>898</v>
       </c>
     </row>
     <row r="31">
@@ -1573,37 +1573,37 @@
         <v>36</v>
       </c>
       <c r="B31" t="n">
-        <v>1247</v>
+        <v>936</v>
       </c>
       <c r="C31" t="n">
-        <v>884</v>
+        <v>981</v>
       </c>
       <c r="D31" t="n">
-        <v>918</v>
+        <v>1054</v>
       </c>
       <c r="E31" t="n">
-        <v>1046</v>
+        <v>945</v>
       </c>
       <c r="F31" t="n">
-        <v>1255</v>
+        <v>1019</v>
       </c>
       <c r="G31" t="n">
-        <v>1059</v>
+        <v>903</v>
       </c>
       <c r="H31" t="n">
-        <v>1069</v>
+        <v>789</v>
       </c>
       <c r="I31" t="n">
-        <v>981</v>
+        <v>965</v>
       </c>
       <c r="J31" t="n">
-        <v>966</v>
+        <v>1099</v>
       </c>
       <c r="K31" t="n">
-        <v>1043</v>
+        <v>886</v>
       </c>
       <c r="L31" t="n">
-        <v>1046.8</v>
+        <v>957.7</v>
       </c>
     </row>
     <row r="32">
@@ -1611,37 +1611,37 @@
         <v>37</v>
       </c>
       <c r="B32" t="n">
-        <v>1099</v>
+        <v>994</v>
       </c>
       <c r="C32" t="n">
-        <v>1050</v>
+        <v>1091</v>
       </c>
       <c r="D32" t="n">
-        <v>1082</v>
+        <v>1166</v>
       </c>
       <c r="E32" t="n">
-        <v>1016</v>
+        <v>1063</v>
       </c>
       <c r="F32" t="n">
-        <v>1076</v>
+        <v>1021</v>
       </c>
       <c r="G32" t="n">
-        <v>1252</v>
+        <v>1133</v>
       </c>
       <c r="H32" t="n">
-        <v>1097</v>
+        <v>1100</v>
       </c>
       <c r="I32" t="n">
-        <v>1247</v>
+        <v>1004</v>
       </c>
       <c r="J32" t="n">
-        <v>1097</v>
+        <v>988</v>
       </c>
       <c r="K32" t="n">
-        <v>1090</v>
+        <v>1126</v>
       </c>
       <c r="L32" t="n">
-        <v>1110.6</v>
+        <v>1068.6</v>
       </c>
     </row>
     <row r="33">
@@ -1649,37 +1649,37 @@
         <v>38</v>
       </c>
       <c r="B33" t="n">
+        <v>993</v>
+      </c>
+      <c r="C33" t="n">
+        <v>1016</v>
+      </c>
+      <c r="D33" t="n">
+        <v>920</v>
+      </c>
+      <c r="E33" t="n">
+        <v>914</v>
+      </c>
+      <c r="F33" t="n">
         <v>904</v>
       </c>
-      <c r="C33" t="n">
-        <v>994</v>
-      </c>
-      <c r="D33" t="n">
-        <v>928</v>
-      </c>
-      <c r="E33" t="n">
-        <v>1075</v>
-      </c>
-      <c r="F33" t="n">
-        <v>1000</v>
-      </c>
       <c r="G33" t="n">
-        <v>1077</v>
+        <v>929</v>
       </c>
       <c r="H33" t="n">
-        <v>906</v>
+        <v>978</v>
       </c>
       <c r="I33" t="n">
-        <v>987</v>
+        <v>985</v>
       </c>
       <c r="J33" t="n">
-        <v>1008</v>
+        <v>904</v>
       </c>
       <c r="K33" t="n">
-        <v>952</v>
+        <v>890</v>
       </c>
       <c r="L33" t="n">
-        <v>983.1</v>
+        <v>943.3</v>
       </c>
     </row>
     <row r="34">
@@ -1687,37 +1687,37 @@
         <v>39</v>
       </c>
       <c r="B34" t="n">
-        <v>997</v>
+        <v>945</v>
       </c>
       <c r="C34" t="n">
-        <v>1153</v>
+        <v>961</v>
       </c>
       <c r="D34" t="n">
-        <v>995</v>
+        <v>876</v>
       </c>
       <c r="E34" t="n">
-        <v>1197</v>
+        <v>952</v>
       </c>
       <c r="F34" t="n">
-        <v>1032</v>
+        <v>933</v>
       </c>
       <c r="G34" t="n">
-        <v>998</v>
+        <v>1013</v>
       </c>
       <c r="H34" t="n">
-        <v>1169</v>
+        <v>963</v>
       </c>
       <c r="I34" t="n">
-        <v>1137</v>
+        <v>1062</v>
       </c>
       <c r="J34" t="n">
-        <v>1043</v>
+        <v>989</v>
       </c>
       <c r="K34" t="n">
-        <v>970</v>
+        <v>984</v>
       </c>
       <c r="L34" t="n">
-        <v>1069.1</v>
+        <v>967.8</v>
       </c>
     </row>
     <row r="35">
@@ -1725,37 +1725,37 @@
         <v>4</v>
       </c>
       <c r="B35" t="n">
-        <v>1015</v>
+        <v>961</v>
       </c>
       <c r="C35" t="n">
-        <v>1016</v>
+        <v>986</v>
       </c>
       <c r="D35" t="n">
-        <v>1355</v>
+        <v>889</v>
       </c>
       <c r="E35" t="n">
-        <v>1066</v>
+        <v>1013</v>
       </c>
       <c r="F35" t="n">
-        <v>1165</v>
+        <v>927</v>
       </c>
       <c r="G35" t="n">
-        <v>1174</v>
+        <v>859</v>
       </c>
       <c r="H35" t="n">
-        <v>1194</v>
+        <v>1148</v>
       </c>
       <c r="I35" t="n">
-        <v>1086</v>
+        <v>904</v>
       </c>
       <c r="J35" t="n">
-        <v>1140</v>
+        <v>968</v>
       </c>
       <c r="K35" t="n">
-        <v>1123</v>
+        <v>1027</v>
       </c>
       <c r="L35" t="n">
-        <v>1133.4</v>
+        <v>968.2</v>
       </c>
     </row>
     <row r="36">
@@ -1763,37 +1763,37 @@
         <v>40</v>
       </c>
       <c r="B36" t="n">
-        <v>1343</v>
+        <v>1104</v>
       </c>
       <c r="C36" t="n">
-        <v>974</v>
+        <v>959</v>
       </c>
       <c r="D36" t="n">
-        <v>1059</v>
+        <v>971</v>
       </c>
       <c r="E36" t="n">
-        <v>1111</v>
+        <v>1019</v>
       </c>
       <c r="F36" t="n">
-        <v>1199</v>
+        <v>1034</v>
       </c>
       <c r="G36" t="n">
-        <v>1001</v>
+        <v>964</v>
       </c>
       <c r="H36" t="n">
-        <v>1043</v>
+        <v>1003</v>
       </c>
       <c r="I36" t="n">
-        <v>901</v>
+        <v>956</v>
       </c>
       <c r="J36" t="n">
-        <v>1133</v>
+        <v>1016</v>
       </c>
       <c r="K36" t="n">
-        <v>1279</v>
+        <v>913</v>
       </c>
       <c r="L36" t="n">
-        <v>1104.3</v>
+        <v>993.9</v>
       </c>
     </row>
     <row r="37">
@@ -1801,37 +1801,37 @@
         <v>41</v>
       </c>
       <c r="B37" t="n">
-        <v>1069</v>
+        <v>985</v>
       </c>
       <c r="C37" t="n">
-        <v>1053</v>
+        <v>923</v>
       </c>
       <c r="D37" t="n">
-        <v>922</v>
+        <v>826</v>
       </c>
       <c r="E37" t="n">
-        <v>1082</v>
+        <v>967</v>
       </c>
       <c r="F37" t="n">
-        <v>984</v>
+        <v>957</v>
       </c>
       <c r="G37" t="n">
-        <v>1057</v>
+        <v>889</v>
       </c>
       <c r="H37" t="n">
-        <v>1025</v>
+        <v>893</v>
       </c>
       <c r="I37" t="n">
-        <v>1089</v>
+        <v>916</v>
       </c>
       <c r="J37" t="n">
         <v>847</v>
       </c>
       <c r="K37" t="n">
-        <v>1022</v>
+        <v>974</v>
       </c>
       <c r="L37" t="n">
-        <v>1015</v>
+        <v>917.7</v>
       </c>
     </row>
     <row r="38">
@@ -1839,37 +1839,37 @@
         <v>42</v>
       </c>
       <c r="B38" t="n">
-        <v>853</v>
+        <v>780</v>
       </c>
       <c r="C38" t="n">
+        <v>847</v>
+      </c>
+      <c r="D38" t="n">
+        <v>820</v>
+      </c>
+      <c r="E38" t="n">
+        <v>829</v>
+      </c>
+      <c r="F38" t="n">
         <v>872</v>
       </c>
-      <c r="D38" t="n">
-        <v>882</v>
-      </c>
-      <c r="E38" t="n">
-        <v>846</v>
-      </c>
-      <c r="F38" t="n">
-        <v>923</v>
-      </c>
       <c r="G38" t="n">
-        <v>873</v>
+        <v>886</v>
       </c>
       <c r="H38" t="n">
-        <v>997</v>
+        <v>836</v>
       </c>
       <c r="I38" t="n">
-        <v>887</v>
+        <v>886</v>
       </c>
       <c r="J38" t="n">
-        <v>1050</v>
+        <v>959</v>
       </c>
       <c r="K38" t="n">
-        <v>971</v>
+        <v>986</v>
       </c>
       <c r="L38" t="n">
-        <v>915.4</v>
+        <v>870.1</v>
       </c>
     </row>
     <row r="39">
@@ -1877,37 +1877,37 @@
         <v>43</v>
       </c>
       <c r="B39" t="n">
-        <v>1046</v>
+        <v>817</v>
       </c>
       <c r="C39" t="n">
-        <v>1162</v>
+        <v>1005</v>
       </c>
       <c r="D39" t="n">
-        <v>934</v>
+        <v>971</v>
       </c>
       <c r="E39" t="n">
-        <v>1006</v>
+        <v>983</v>
       </c>
       <c r="F39" t="n">
-        <v>956</v>
+        <v>799</v>
       </c>
       <c r="G39" t="n">
-        <v>884</v>
+        <v>964</v>
       </c>
       <c r="H39" t="n">
-        <v>1125</v>
+        <v>953</v>
       </c>
       <c r="I39" t="n">
-        <v>1118</v>
+        <v>899</v>
       </c>
       <c r="J39" t="n">
-        <v>1220</v>
+        <v>1039</v>
       </c>
       <c r="K39" t="n">
-        <v>1301</v>
+        <v>988</v>
       </c>
       <c r="L39" t="n">
-        <v>1075.2</v>
+        <v>941.8</v>
       </c>
     </row>
     <row r="40">
@@ -1915,37 +1915,37 @@
         <v>44</v>
       </c>
       <c r="B40" t="n">
-        <v>1039</v>
+        <v>912</v>
       </c>
       <c r="C40" t="n">
-        <v>947</v>
+        <v>853</v>
       </c>
       <c r="D40" t="n">
-        <v>1058</v>
+        <v>914</v>
       </c>
       <c r="E40" t="n">
-        <v>970</v>
+        <v>923</v>
       </c>
       <c r="F40" t="n">
-        <v>922</v>
+        <v>895</v>
       </c>
       <c r="G40" t="n">
-        <v>1203</v>
+        <v>868</v>
       </c>
       <c r="H40" t="n">
-        <v>1050</v>
+        <v>904</v>
       </c>
       <c r="I40" t="n">
-        <v>936</v>
+        <v>790</v>
       </c>
       <c r="J40" t="n">
-        <v>834</v>
+        <v>933</v>
       </c>
       <c r="K40" t="n">
-        <v>952</v>
+        <v>949</v>
       </c>
       <c r="L40" t="n">
-        <v>991.1</v>
+        <v>894.1</v>
       </c>
     </row>
     <row r="41">
@@ -1953,37 +1953,37 @@
         <v>45</v>
       </c>
       <c r="B41" t="n">
-        <v>1214</v>
+        <v>722</v>
       </c>
       <c r="C41" t="n">
-        <v>1098</v>
+        <v>885</v>
       </c>
       <c r="D41" t="n">
-        <v>787</v>
+        <v>823</v>
       </c>
       <c r="E41" t="n">
-        <v>969</v>
+        <v>777</v>
       </c>
       <c r="F41" t="n">
-        <v>1145</v>
+        <v>802</v>
       </c>
       <c r="G41" t="n">
-        <v>1174</v>
+        <v>836</v>
       </c>
       <c r="H41" t="n">
-        <v>895</v>
+        <v>773</v>
       </c>
       <c r="I41" t="n">
-        <v>852</v>
+        <v>814</v>
       </c>
       <c r="J41" t="n">
-        <v>984</v>
+        <v>873</v>
       </c>
       <c r="K41" t="n">
-        <v>913</v>
+        <v>840</v>
       </c>
       <c r="L41" t="n">
-        <v>1003.1</v>
+        <v>814.5</v>
       </c>
     </row>
     <row r="42">
@@ -1991,37 +1991,37 @@
         <v>46</v>
       </c>
       <c r="B42" t="n">
-        <v>940</v>
+        <v>827</v>
       </c>
       <c r="C42" t="n">
-        <v>1249</v>
+        <v>952</v>
       </c>
       <c r="D42" t="n">
-        <v>960</v>
+        <v>915</v>
       </c>
       <c r="E42" t="n">
-        <v>1037</v>
+        <v>818</v>
       </c>
       <c r="F42" t="n">
-        <v>971</v>
+        <v>910</v>
       </c>
       <c r="G42" t="n">
-        <v>1005</v>
+        <v>829</v>
       </c>
       <c r="H42" t="n">
-        <v>885</v>
+        <v>915</v>
       </c>
       <c r="I42" t="n">
-        <v>955</v>
+        <v>944</v>
       </c>
       <c r="J42" t="n">
-        <v>1070</v>
+        <v>844</v>
       </c>
       <c r="K42" t="n">
-        <v>1072</v>
+        <v>933</v>
       </c>
       <c r="L42" t="n">
-        <v>1014.4</v>
+        <v>888.7</v>
       </c>
     </row>
     <row r="43">
@@ -2029,37 +2029,37 @@
         <v>47</v>
       </c>
       <c r="B43" t="n">
-        <v>952</v>
+        <v>888</v>
       </c>
       <c r="C43" t="n">
-        <v>1074</v>
+        <v>829</v>
       </c>
       <c r="D43" t="n">
-        <v>1033</v>
+        <v>886</v>
       </c>
       <c r="E43" t="n">
-        <v>1050</v>
+        <v>847</v>
       </c>
       <c r="F43" t="n">
-        <v>845</v>
+        <v>849</v>
       </c>
       <c r="G43" t="n">
-        <v>886</v>
+        <v>900</v>
       </c>
       <c r="H43" t="n">
-        <v>1031</v>
+        <v>807</v>
       </c>
       <c r="I43" t="n">
-        <v>904</v>
+        <v>902</v>
       </c>
       <c r="J43" t="n">
-        <v>1011</v>
+        <v>850</v>
       </c>
       <c r="K43" t="n">
-        <v>844</v>
+        <v>971</v>
       </c>
       <c r="L43" t="n">
-        <v>963</v>
+        <v>872.9</v>
       </c>
     </row>
     <row r="44">
@@ -2067,37 +2067,37 @@
         <v>48</v>
       </c>
       <c r="B44" t="n">
-        <v>873</v>
+        <v>854</v>
       </c>
       <c r="C44" t="n">
-        <v>1064</v>
+        <v>913</v>
       </c>
       <c r="D44" t="n">
-        <v>906</v>
+        <v>818</v>
       </c>
       <c r="E44" t="n">
-        <v>924</v>
+        <v>899</v>
       </c>
       <c r="F44" t="n">
-        <v>1129</v>
+        <v>868</v>
       </c>
       <c r="G44" t="n">
-        <v>970</v>
+        <v>870</v>
       </c>
       <c r="H44" t="n">
-        <v>1089</v>
+        <v>907</v>
       </c>
       <c r="I44" t="n">
-        <v>1139</v>
+        <v>902</v>
       </c>
       <c r="J44" t="n">
-        <v>1040</v>
+        <v>758</v>
       </c>
       <c r="K44" t="n">
-        <v>867</v>
+        <v>856</v>
       </c>
       <c r="L44" t="n">
-        <v>1000.1</v>
+        <v>864.5</v>
       </c>
     </row>
     <row r="45">
@@ -2105,37 +2105,37 @@
         <v>49</v>
       </c>
       <c r="B45" t="n">
-        <v>1062</v>
+        <v>1051</v>
       </c>
       <c r="C45" t="n">
-        <v>1118</v>
+        <v>1110</v>
       </c>
       <c r="D45" t="n">
-        <v>1290</v>
+        <v>1057</v>
       </c>
       <c r="E45" t="n">
-        <v>1016</v>
+        <v>1033</v>
       </c>
       <c r="F45" t="n">
-        <v>1035</v>
+        <v>1129</v>
       </c>
       <c r="G45" t="n">
-        <v>1084</v>
+        <v>1024</v>
       </c>
       <c r="H45" t="n">
-        <v>1142</v>
+        <v>1096</v>
       </c>
       <c r="I45" t="n">
-        <v>1131</v>
+        <v>1064</v>
       </c>
       <c r="J45" t="n">
-        <v>1009</v>
+        <v>1243</v>
       </c>
       <c r="K45" t="n">
-        <v>1287</v>
+        <v>1179</v>
       </c>
       <c r="L45" t="n">
-        <v>1117.4</v>
+        <v>1098.6</v>
       </c>
     </row>
     <row r="46">
@@ -2143,37 +2143,37 @@
         <v>5</v>
       </c>
       <c r="B46" t="n">
-        <v>991</v>
+        <v>869</v>
       </c>
       <c r="C46" t="n">
-        <v>1088</v>
+        <v>905</v>
       </c>
       <c r="D46" t="n">
-        <v>1017</v>
+        <v>786</v>
       </c>
       <c r="E46" t="n">
-        <v>853</v>
+        <v>886</v>
       </c>
       <c r="F46" t="n">
-        <v>872</v>
+        <v>1031</v>
       </c>
       <c r="G46" t="n">
-        <v>1086</v>
+        <v>1087</v>
       </c>
       <c r="H46" t="n">
-        <v>1119</v>
+        <v>913</v>
       </c>
       <c r="I46" t="n">
-        <v>1052</v>
+        <v>995</v>
       </c>
       <c r="J46" t="n">
-        <v>942</v>
+        <v>940</v>
       </c>
       <c r="K46" t="n">
-        <v>840</v>
+        <v>1011</v>
       </c>
       <c r="L46" t="n">
-        <v>986</v>
+        <v>942.3</v>
       </c>
     </row>
     <row r="47">
@@ -2181,37 +2181,37 @@
         <v>50</v>
       </c>
       <c r="B47" t="n">
-        <v>1038</v>
+        <v>1008</v>
       </c>
       <c r="C47" t="n">
-        <v>1243</v>
+        <v>899</v>
       </c>
       <c r="D47" t="n">
-        <v>1119</v>
+        <v>1027</v>
       </c>
       <c r="E47" t="n">
-        <v>1196</v>
+        <v>1069</v>
       </c>
       <c r="F47" t="n">
-        <v>1057</v>
+        <v>1045</v>
       </c>
       <c r="G47" t="n">
-        <v>1063</v>
+        <v>952</v>
       </c>
       <c r="H47" t="n">
-        <v>1084</v>
+        <v>867</v>
       </c>
       <c r="I47" t="n">
-        <v>1001</v>
+        <v>1081</v>
       </c>
       <c r="J47" t="n">
-        <v>1114</v>
+        <v>982</v>
       </c>
       <c r="K47" t="n">
-        <v>1114</v>
+        <v>898</v>
       </c>
       <c r="L47" t="n">
-        <v>1102.9</v>
+        <v>982.8</v>
       </c>
     </row>
     <row r="48">
@@ -2219,37 +2219,37 @@
         <v>6</v>
       </c>
       <c r="B48" t="n">
-        <v>970</v>
+        <v>883</v>
       </c>
       <c r="C48" t="n">
-        <v>799</v>
+        <v>865</v>
       </c>
       <c r="D48" t="n">
-        <v>990</v>
+        <v>843</v>
       </c>
       <c r="E48" t="n">
-        <v>939</v>
+        <v>947</v>
       </c>
       <c r="F48" t="n">
-        <v>1026</v>
+        <v>925</v>
       </c>
       <c r="G48" t="n">
-        <v>1042</v>
+        <v>819</v>
       </c>
       <c r="H48" t="n">
-        <v>829</v>
+        <v>780</v>
       </c>
       <c r="I48" t="n">
-        <v>1035</v>
+        <v>860</v>
       </c>
       <c r="J48" t="n">
-        <v>884</v>
+        <v>864</v>
       </c>
       <c r="K48" t="n">
-        <v>920</v>
+        <v>900</v>
       </c>
       <c r="L48" t="n">
-        <v>943.4</v>
+        <v>868.6</v>
       </c>
     </row>
     <row r="49">
@@ -2257,37 +2257,37 @@
         <v>7</v>
       </c>
       <c r="B49" t="n">
-        <v>973</v>
+        <v>776</v>
       </c>
       <c r="C49" t="n">
-        <v>987</v>
+        <v>1025</v>
       </c>
       <c r="D49" t="n">
-        <v>1076</v>
+        <v>937</v>
       </c>
       <c r="E49" t="n">
-        <v>1066</v>
+        <v>826</v>
       </c>
       <c r="F49" t="n">
-        <v>1121</v>
+        <v>865</v>
       </c>
       <c r="G49" t="n">
-        <v>940</v>
+        <v>887</v>
       </c>
       <c r="H49" t="n">
-        <v>1022</v>
+        <v>919</v>
       </c>
       <c r="I49" t="n">
-        <v>1068</v>
+        <v>1053</v>
       </c>
       <c r="J49" t="n">
-        <v>978</v>
+        <v>1040</v>
       </c>
       <c r="K49" t="n">
-        <v>1012</v>
+        <v>953</v>
       </c>
       <c r="L49" t="n">
-        <v>1024.3</v>
+        <v>928.1</v>
       </c>
     </row>
     <row r="50">
@@ -2295,37 +2295,37 @@
         <v>8</v>
       </c>
       <c r="B50" t="n">
-        <v>913</v>
+        <v>961</v>
       </c>
       <c r="C50" t="n">
-        <v>1149</v>
+        <v>971</v>
       </c>
       <c r="D50" t="n">
-        <v>976</v>
+        <v>908</v>
       </c>
       <c r="E50" t="n">
-        <v>955</v>
+        <v>965</v>
       </c>
       <c r="F50" t="n">
-        <v>1201</v>
+        <v>944</v>
       </c>
       <c r="G50" t="n">
-        <v>946</v>
+        <v>930</v>
       </c>
       <c r="H50" t="n">
-        <v>947</v>
+        <v>1072</v>
       </c>
       <c r="I50" t="n">
-        <v>1105</v>
+        <v>874</v>
       </c>
       <c r="J50" t="n">
-        <v>891</v>
+        <v>1052</v>
       </c>
       <c r="K50" t="n">
-        <v>1193</v>
+        <v>905</v>
       </c>
       <c r="L50" t="n">
-        <v>1027.6</v>
+        <v>958.2</v>
       </c>
     </row>
     <row r="51">
@@ -2333,37 +2333,37 @@
         <v>9</v>
       </c>
       <c r="B51" t="n">
-        <v>1135</v>
+        <v>1161</v>
       </c>
       <c r="C51" t="n">
-        <v>922</v>
+        <v>875</v>
       </c>
       <c r="D51" t="n">
-        <v>1079</v>
+        <v>887</v>
       </c>
       <c r="E51" t="n">
-        <v>1029</v>
+        <v>790</v>
       </c>
       <c r="F51" t="n">
-        <v>966</v>
+        <v>927</v>
       </c>
       <c r="G51" t="n">
-        <v>1141</v>
+        <v>976</v>
       </c>
       <c r="H51" t="n">
-        <v>1215</v>
+        <v>785</v>
       </c>
       <c r="I51" t="n">
-        <v>1059</v>
+        <v>874</v>
       </c>
       <c r="J51" t="n">
-        <v>906</v>
+        <v>927</v>
       </c>
       <c r="K51" t="n">
-        <v>1254</v>
+        <v>945</v>
       </c>
       <c r="L51" t="n">
-        <v>1070.6</v>
+        <v>914.7</v>
       </c>
     </row>
     <row r="52">
@@ -2373,37 +2373,37 @@
         </is>
       </c>
       <c r="B52" t="n">
-        <v>1031.52</v>
+        <v>931.8200000000001</v>
       </c>
       <c r="C52" t="n">
-        <v>1022.42</v>
+        <v>946</v>
       </c>
       <c r="D52" t="n">
-        <v>1036.22</v>
+        <v>925.6</v>
       </c>
       <c r="E52" t="n">
-        <v>1041.92</v>
+        <v>930.7</v>
       </c>
       <c r="F52" t="n">
-        <v>1041.18</v>
+        <v>924.92</v>
       </c>
       <c r="G52" t="n">
-        <v>1041.28</v>
+        <v>939.08</v>
       </c>
       <c r="H52" t="n">
-        <v>1033.94</v>
+        <v>927.24</v>
       </c>
       <c r="I52" t="n">
-        <v>1038.28</v>
+        <v>939.92</v>
       </c>
       <c r="J52" t="n">
-        <v>1041.5</v>
+        <v>934.8200000000001</v>
       </c>
       <c r="K52" t="n">
-        <v>1063.2</v>
+        <v>960.42</v>
       </c>
       <c r="L52" t="n">
-        <v>1039.146</v>
+        <v>936.052</v>
       </c>
     </row>
   </sheetData>
@@ -2462,37 +2462,37 @@
         <v>1</v>
       </c>
       <c r="B2" t="n">
-        <v>10.4598503112793</v>
+        <v>8.493948221206665</v>
       </c>
       <c r="C2" t="n">
-        <v>9.369647741317749</v>
+        <v>9.567544937133789</v>
       </c>
       <c r="D2" t="n">
-        <v>8.291409254074097</v>
+        <v>9.077920913696289</v>
       </c>
       <c r="E2" t="n">
-        <v>7.993518590927124</v>
+        <v>9.289482593536377</v>
       </c>
       <c r="F2" t="n">
-        <v>7.935269832611084</v>
+        <v>8.702096700668335</v>
       </c>
       <c r="G2" t="n">
-        <v>7.887401342391968</v>
+        <v>9.361490488052368</v>
       </c>
       <c r="H2" t="n">
-        <v>7.80911111831665</v>
+        <v>8.668443918228149</v>
       </c>
       <c r="I2" t="n">
-        <v>9.089441537857056</v>
+        <v>9.187483072280884</v>
       </c>
       <c r="J2" t="n">
-        <v>7.79013204574585</v>
+        <v>8.263501644134521</v>
       </c>
       <c r="K2" t="n">
-        <v>8.262470960617065</v>
+        <v>9.289993524551392</v>
       </c>
       <c r="L2" t="n">
-        <v>8.488825273513793</v>
+        <v>8.990190601348877</v>
       </c>
     </row>
     <row r="3">
@@ -2500,37 +2500,37 @@
         <v>10</v>
       </c>
       <c r="B3" t="n">
-        <v>7.585180759429932</v>
+        <v>9.320504426956177</v>
       </c>
       <c r="C3" t="n">
-        <v>8.844014406204224</v>
+        <v>9.469954013824463</v>
       </c>
       <c r="D3" t="n">
-        <v>10.15562152862549</v>
+        <v>9.440586090087891</v>
       </c>
       <c r="E3" t="n">
-        <v>7.939273118972778</v>
+        <v>8.331588268280029</v>
       </c>
       <c r="F3" t="n">
-        <v>7.284963130950928</v>
+        <v>7.726010084152222</v>
       </c>
       <c r="G3" t="n">
-        <v>8.231996059417725</v>
+        <v>8.485366344451904</v>
       </c>
       <c r="H3" t="n">
-        <v>7.505362033843994</v>
+        <v>9.673935174942017</v>
       </c>
       <c r="I3" t="n">
-        <v>7.782186985015869</v>
+        <v>8.415040731430054</v>
       </c>
       <c r="J3" t="n">
-        <v>9.250462293624878</v>
+        <v>9.350527048110962</v>
       </c>
       <c r="K3" t="n">
-        <v>9.520225763320923</v>
+        <v>8.280994415283203</v>
       </c>
       <c r="L3" t="n">
-        <v>8.409928607940675</v>
+        <v>8.849450659751891</v>
       </c>
     </row>
     <row r="4">
@@ -2538,37 +2538,37 @@
         <v>11</v>
       </c>
       <c r="B4" t="n">
-        <v>7.428061008453369</v>
+        <v>8.476967096328735</v>
       </c>
       <c r="C4" t="n">
-        <v>7.868486881256104</v>
+        <v>8.424544811248779</v>
       </c>
       <c r="D4" t="n">
-        <v>8.657011985778809</v>
+        <v>8.094713687896729</v>
       </c>
       <c r="E4" t="n">
-        <v>13.50738191604614</v>
+        <v>8.830082178115845</v>
       </c>
       <c r="F4" t="n">
-        <v>7.987729787826538</v>
+        <v>7.919147253036499</v>
       </c>
       <c r="G4" t="n">
-        <v>8.143306493759155</v>
+        <v>9.089025974273682</v>
       </c>
       <c r="H4" t="n">
-        <v>8.278451681137085</v>
+        <v>8.560530662536621</v>
       </c>
       <c r="I4" t="n">
-        <v>9.645016193389893</v>
+        <v>9.225937366485596</v>
       </c>
       <c r="J4" t="n">
-        <v>7.913321733474731</v>
+        <v>8.634837627410889</v>
       </c>
       <c r="K4" t="n">
-        <v>8.613531589508057</v>
+        <v>9.238589763641357</v>
       </c>
       <c r="L4" t="n">
-        <v>8.804229927062988</v>
+        <v>8.649437642097473</v>
       </c>
     </row>
     <row r="5">
@@ -2576,37 +2576,37 @@
         <v>12</v>
       </c>
       <c r="B5" t="n">
-        <v>10.6094491481781</v>
+        <v>8.884570598602295</v>
       </c>
       <c r="C5" t="n">
-        <v>7.008157730102539</v>
+        <v>8.029384613037109</v>
       </c>
       <c r="D5" t="n">
-        <v>7.031067371368408</v>
+        <v>6.838182926177979</v>
       </c>
       <c r="E5" t="n">
-        <v>7.128837108612061</v>
+        <v>7.6091628074646</v>
       </c>
       <c r="F5" t="n">
-        <v>10.30874729156494</v>
+        <v>7.670487403869629</v>
       </c>
       <c r="G5" t="n">
-        <v>7.85161280632019</v>
+        <v>8.387085437774658</v>
       </c>
       <c r="H5" t="n">
-        <v>7.617653608322144</v>
+        <v>7.112977743148804</v>
       </c>
       <c r="I5" t="n">
-        <v>8.968623638153076</v>
+        <v>7.324412822723389</v>
       </c>
       <c r="J5" t="n">
-        <v>7.576696395874023</v>
+        <v>7.072087049484253</v>
       </c>
       <c r="K5" t="n">
-        <v>8.508822202682495</v>
+        <v>8.226444005966187</v>
       </c>
       <c r="L5" t="n">
-        <v>8.260966730117797</v>
+        <v>7.71547954082489</v>
       </c>
     </row>
     <row r="6">
@@ -2614,37 +2614,37 @@
         <v>13</v>
       </c>
       <c r="B6" t="n">
-        <v>7.52434778213501</v>
+        <v>8.682780742645264</v>
       </c>
       <c r="C6" t="n">
-        <v>8.691361427307129</v>
+        <v>7.583118677139282</v>
       </c>
       <c r="D6" t="n">
-        <v>7.231577634811401</v>
+        <v>6.875613451004028</v>
       </c>
       <c r="E6" t="n">
-        <v>8.425539255142212</v>
+        <v>7.506924390792847</v>
       </c>
       <c r="F6" t="n">
-        <v>9.041936159133911</v>
+        <v>7.495099544525146</v>
       </c>
       <c r="G6" t="n">
-        <v>10.05536937713623</v>
+        <v>7.926802635192871</v>
       </c>
       <c r="H6" t="n">
-        <v>9.917207002639771</v>
+        <v>8.197079181671143</v>
       </c>
       <c r="I6" t="n">
-        <v>7.610591173171997</v>
+        <v>9.056299209594727</v>
       </c>
       <c r="J6" t="n">
-        <v>10.22693228721619</v>
+        <v>8.133249998092651</v>
       </c>
       <c r="K6" t="n">
-        <v>9.049471378326416</v>
+        <v>8.749601364135742</v>
       </c>
       <c r="L6" t="n">
-        <v>8.777433347702026</v>
+        <v>8.02065691947937</v>
       </c>
     </row>
     <row r="7">
@@ -2652,37 +2652,37 @@
         <v>14</v>
       </c>
       <c r="B7" t="n">
-        <v>8.563724517822266</v>
+        <v>10.37924408912659</v>
       </c>
       <c r="C7" t="n">
-        <v>7.989639043807983</v>
+        <v>9.169477939605713</v>
       </c>
       <c r="D7" t="n">
-        <v>8.479395151138306</v>
+        <v>8.813430547714233</v>
       </c>
       <c r="E7" t="n">
-        <v>8.437031745910645</v>
+        <v>8.679578065872192</v>
       </c>
       <c r="F7" t="n">
-        <v>8.242987394332886</v>
+        <v>10.78598546981812</v>
       </c>
       <c r="G7" t="n">
-        <v>9.561144351959229</v>
+        <v>8.854321956634521</v>
       </c>
       <c r="H7" t="n">
-        <v>7.745266199111938</v>
+        <v>8.590418100357056</v>
       </c>
       <c r="I7" t="n">
-        <v>9.517227172851562</v>
+        <v>7.609456062316895</v>
       </c>
       <c r="J7" t="n">
-        <v>7.766694784164429</v>
+        <v>7.364306926727295</v>
       </c>
       <c r="K7" t="n">
-        <v>7.975679397583008</v>
+        <v>8.701671600341797</v>
       </c>
       <c r="L7" t="n">
-        <v>8.427878975868225</v>
+        <v>8.89478907585144</v>
       </c>
     </row>
     <row r="8">
@@ -2690,37 +2690,37 @@
         <v>15</v>
       </c>
       <c r="B8" t="n">
-        <v>8.789092779159546</v>
+        <v>10.13589406013489</v>
       </c>
       <c r="C8" t="n">
-        <v>9.325717210769653</v>
+        <v>10.91393232345581</v>
       </c>
       <c r="D8" t="n">
-        <v>7.789191484451294</v>
+        <v>8.47234320640564</v>
       </c>
       <c r="E8" t="n">
-        <v>9.330784320831299</v>
+        <v>8.195085048675537</v>
       </c>
       <c r="F8" t="n">
-        <v>8.381649494171143</v>
+        <v>7.86696195602417</v>
       </c>
       <c r="G8" t="n">
-        <v>8.715295076370239</v>
+        <v>7.577072858810425</v>
       </c>
       <c r="H8" t="n">
-        <v>8.167732238769531</v>
+        <v>8.122278690338135</v>
       </c>
       <c r="I8" t="n">
-        <v>7.971734046936035</v>
+        <v>9.047765016555786</v>
       </c>
       <c r="J8" t="n">
-        <v>11.28326892852783</v>
+        <v>8.414497137069702</v>
       </c>
       <c r="K8" t="n">
-        <v>9.419012546539307</v>
+        <v>8.260908842086792</v>
       </c>
       <c r="L8" t="n">
-        <v>8.917347812652588</v>
+        <v>8.700673913955688</v>
       </c>
     </row>
     <row r="9">
@@ -2728,37 +2728,37 @@
         <v>16</v>
       </c>
       <c r="B9" t="n">
-        <v>9.711229801177979</v>
+        <v>7.5192551612854</v>
       </c>
       <c r="C9" t="n">
-        <v>7.66397500038147</v>
+        <v>7.902314186096191</v>
       </c>
       <c r="D9" t="n">
-        <v>8.302353382110596</v>
+        <v>7.552321672439575</v>
       </c>
       <c r="E9" t="n">
-        <v>8.724584102630615</v>
+        <v>8.009580135345459</v>
       </c>
       <c r="F9" t="n">
-        <v>8.590116024017334</v>
+        <v>7.019229650497437</v>
       </c>
       <c r="G9" t="n">
-        <v>7.277709484100342</v>
+        <v>7.878929853439331</v>
       </c>
       <c r="H9" t="n">
-        <v>8.857426166534424</v>
+        <v>6.807138442993164</v>
       </c>
       <c r="I9" t="n">
-        <v>7.628082990646362</v>
+        <v>7.914834499359131</v>
       </c>
       <c r="J9" t="n">
-        <v>9.34366512298584</v>
+        <v>7.309453248977661</v>
       </c>
       <c r="K9" t="n">
-        <v>8.308306932449341</v>
+        <v>7.991621971130371</v>
       </c>
       <c r="L9" t="n">
-        <v>8.440744900703431</v>
+        <v>7.590467882156372</v>
       </c>
     </row>
     <row r="10">
@@ -2766,37 +2766,37 @@
         <v>17</v>
       </c>
       <c r="B10" t="n">
-        <v>7.395162343978882</v>
+        <v>7.321420669555664</v>
       </c>
       <c r="C10" t="n">
-        <v>8.599574565887451</v>
+        <v>6.941454172134399</v>
       </c>
       <c r="D10" t="n">
-        <v>7.870409488677979</v>
+        <v>7.208722352981567</v>
       </c>
       <c r="E10" t="n">
-        <v>6.97274374961853</v>
+        <v>6.926457166671753</v>
       </c>
       <c r="F10" t="n">
-        <v>7.335312843322754</v>
+        <v>7.127937793731689</v>
       </c>
       <c r="G10" t="n">
-        <v>7.666500568389893</v>
+        <v>6.979212522506714</v>
       </c>
       <c r="H10" t="n">
-        <v>7.000187873840332</v>
+        <v>7.077073812484741</v>
       </c>
       <c r="I10" t="n">
-        <v>8.216046810150146</v>
+        <v>7.496952295303345</v>
       </c>
       <c r="J10" t="n">
-        <v>8.994122982025146</v>
+        <v>7.021903991699219</v>
       </c>
       <c r="K10" t="n">
-        <v>7.404129266738892</v>
+        <v>7.346354484558105</v>
       </c>
       <c r="L10" t="n">
-        <v>7.745419049263001</v>
+        <v>7.14474892616272</v>
       </c>
     </row>
     <row r="11">
@@ -2804,37 +2804,37 @@
         <v>18</v>
       </c>
       <c r="B11" t="n">
-        <v>7.378199577331543</v>
+        <v>7.24325704574585</v>
       </c>
       <c r="C11" t="n">
-        <v>7.283974885940552</v>
+        <v>7.020226955413818</v>
       </c>
       <c r="D11" t="n">
-        <v>6.902403354644775</v>
+        <v>7.33139443397522</v>
       </c>
       <c r="E11" t="n">
-        <v>7.72183632850647</v>
+        <v>6.649218320846558</v>
       </c>
       <c r="F11" t="n">
-        <v>7.301385164260864</v>
+        <v>7.781192064285278</v>
       </c>
       <c r="G11" t="n">
-        <v>6.89096474647522</v>
+        <v>7.018232583999634</v>
       </c>
       <c r="H11" t="n">
-        <v>7.509363412857056</v>
+        <v>7.960710763931274</v>
       </c>
       <c r="I11" t="n">
-        <v>8.801570415496826</v>
+        <v>6.355006456375122</v>
       </c>
       <c r="J11" t="n">
-        <v>7.004197597503662</v>
+        <v>6.427810907363892</v>
       </c>
       <c r="K11" t="n">
-        <v>6.930870532989502</v>
+        <v>7.13093090057373</v>
       </c>
       <c r="L11" t="n">
-        <v>7.372476601600647</v>
+        <v>7.091798043251037</v>
       </c>
     </row>
     <row r="12">
@@ -2842,37 +2842,37 @@
         <v>19</v>
       </c>
       <c r="B12" t="n">
-        <v>9.153391361236572</v>
+        <v>7.984719038009644</v>
       </c>
       <c r="C12" t="n">
-        <v>7.859530925750732</v>
+        <v>7.297310352325439</v>
       </c>
       <c r="D12" t="n">
-        <v>8.042540311813354</v>
+        <v>7.740483522415161</v>
       </c>
       <c r="E12" t="n">
-        <v>9.378250122070312</v>
+        <v>6.749835729598999</v>
       </c>
       <c r="F12" t="n">
-        <v>8.581770658493042</v>
+        <v>7.606328010559082</v>
       </c>
       <c r="G12" t="n">
-        <v>9.199622631072998</v>
+        <v>7.621411323547363</v>
       </c>
       <c r="H12" t="n">
-        <v>9.21352219581604</v>
+        <v>6.961418390274048</v>
       </c>
       <c r="I12" t="n">
-        <v>9.827055931091309</v>
+        <v>6.918375015258789</v>
       </c>
       <c r="J12" t="n">
-        <v>11.41296672821045</v>
+        <v>7.406665325164795</v>
       </c>
       <c r="K12" t="n">
-        <v>11.4659104347229</v>
+        <v>7.917338371276855</v>
       </c>
       <c r="L12" t="n">
-        <v>9.413456130027772</v>
+        <v>7.420388507843017</v>
       </c>
     </row>
     <row r="13">
@@ -2880,37 +2880,37 @@
         <v>2</v>
       </c>
       <c r="B13" t="n">
-        <v>7.722846031188965</v>
+        <v>6.682667255401611</v>
       </c>
       <c r="C13" t="n">
-        <v>8.024661064147949</v>
+        <v>6.71304726600647</v>
       </c>
       <c r="D13" t="n">
-        <v>7.993787050247192</v>
+        <v>7.706392526626587</v>
       </c>
       <c r="E13" t="n">
-        <v>8.328321218490601</v>
+        <v>7.116967439651489</v>
       </c>
       <c r="F13" t="n">
-        <v>8.554250478744507</v>
+        <v>6.414844989776611</v>
       </c>
       <c r="G13" t="n">
-        <v>7.426114559173584</v>
+        <v>8.19608211517334</v>
       </c>
       <c r="H13" t="n">
-        <v>8.698921918869019</v>
+        <v>6.893565654754639</v>
       </c>
       <c r="I13" t="n">
-        <v>8.029071092605591</v>
+        <v>6.689111948013306</v>
       </c>
       <c r="J13" t="n">
-        <v>7.307448387145996</v>
+        <v>7.75547981262207</v>
       </c>
       <c r="K13" t="n">
-        <v>8.583148956298828</v>
+        <v>8.153195858001709</v>
       </c>
       <c r="L13" t="n">
-        <v>8.066857075691223</v>
+        <v>7.232135486602783</v>
       </c>
     </row>
     <row r="14">
@@ -2918,37 +2918,37 @@
         <v>20</v>
       </c>
       <c r="B14" t="n">
-        <v>10.77559351921082</v>
+        <v>8.256919622421265</v>
       </c>
       <c r="C14" t="n">
-        <v>9.165305852890015</v>
+        <v>7.662509441375732</v>
       </c>
       <c r="D14" t="n">
-        <v>9.929234504699707</v>
+        <v>9.050695419311523</v>
       </c>
       <c r="E14" t="n">
-        <v>8.796647310256958</v>
+        <v>7.845942735671997</v>
       </c>
       <c r="F14" t="n">
-        <v>12.44631457328796</v>
+        <v>8.067425727844238</v>
       </c>
       <c r="G14" t="n">
-        <v>8.936836242675781</v>
+        <v>7.326331615447998</v>
       </c>
       <c r="H14" t="n">
-        <v>9.9975426197052</v>
+        <v>9.439645290374756</v>
       </c>
       <c r="I14" t="n">
-        <v>10.29329252243042</v>
+        <v>7.389238834381104</v>
       </c>
       <c r="J14" t="n">
-        <v>10.9776291847229</v>
+        <v>8.557865381240845</v>
       </c>
       <c r="K14" t="n">
-        <v>9.121314525604248</v>
+        <v>10.16880750656128</v>
       </c>
       <c r="L14" t="n">
-        <v>10.0439710855484</v>
+        <v>8.376538157463074</v>
       </c>
     </row>
     <row r="15">
@@ -2956,37 +2956,37 @@
         <v>21</v>
       </c>
       <c r="B15" t="n">
-        <v>10.24696755409241</v>
+        <v>10.62159585952759</v>
       </c>
       <c r="C15" t="n">
-        <v>9.692354679107666</v>
+        <v>8.03950023651123</v>
       </c>
       <c r="D15" t="n">
-        <v>8.55623984336853</v>
+        <v>8.103785514831543</v>
       </c>
       <c r="E15" t="n">
-        <v>10.3961009979248</v>
+        <v>8.941593408584595</v>
       </c>
       <c r="F15" t="n">
-        <v>7.690969228744507</v>
+        <v>7.968184232711792</v>
       </c>
       <c r="G15" t="n">
-        <v>7.774771213531494</v>
+        <v>7.809116363525391</v>
       </c>
       <c r="H15" t="n">
-        <v>9.922707557678223</v>
+        <v>8.741726636886597</v>
       </c>
       <c r="I15" t="n">
-        <v>9.105803251266479</v>
+        <v>9.438759803771973</v>
       </c>
       <c r="J15" t="n">
-        <v>9.602998495101929</v>
+        <v>9.022871255874634</v>
       </c>
       <c r="K15" t="n">
-        <v>9.114268064498901</v>
+        <v>8.121472835540771</v>
       </c>
       <c r="L15" t="n">
-        <v>9.210318088531494</v>
+        <v>8.680860614776611</v>
       </c>
     </row>
     <row r="16">
@@ -2994,37 +2994,37 @@
         <v>22</v>
       </c>
       <c r="B16" t="n">
-        <v>7.913402080535889</v>
+        <v>7.842405319213867</v>
       </c>
       <c r="C16" t="n">
-        <v>8.369209289550781</v>
+        <v>8.765559673309326</v>
       </c>
       <c r="D16" t="n">
-        <v>8.143343687057495</v>
+        <v>7.848012924194336</v>
       </c>
       <c r="E16" t="n">
-        <v>10.30734801292419</v>
+        <v>7.456061124801636</v>
       </c>
       <c r="F16" t="n">
-        <v>8.203094720840454</v>
+        <v>8.97967004776001</v>
       </c>
       <c r="G16" t="n">
-        <v>7.394157886505127</v>
+        <v>7.115969657897949</v>
       </c>
       <c r="H16" t="n">
-        <v>8.020571231842041</v>
+        <v>7.662509441375732</v>
       </c>
       <c r="I16" t="n">
-        <v>7.655519247055054</v>
+        <v>7.193763256072998</v>
       </c>
       <c r="J16" t="n">
-        <v>7.824066162109375</v>
+        <v>7.396727085113525</v>
       </c>
       <c r="K16" t="n">
-        <v>7.465458631515503</v>
+        <v>8.646876335144043</v>
       </c>
       <c r="L16" t="n">
-        <v>8.129617094993591</v>
+        <v>7.890755486488342</v>
       </c>
     </row>
     <row r="17">
@@ -3032,37 +3032,37 @@
         <v>23</v>
       </c>
       <c r="B17" t="n">
-        <v>8.291392087936401</v>
+        <v>7.274546146392822</v>
       </c>
       <c r="C17" t="n">
-        <v>8.288860082626343</v>
+        <v>7.466033935546875</v>
       </c>
       <c r="D17" t="n">
-        <v>8.259447574615479</v>
+        <v>8.418486833572388</v>
       </c>
       <c r="E17" t="n">
-        <v>9.470853567123413</v>
+        <v>7.873943328857422</v>
       </c>
       <c r="F17" t="n">
-        <v>9.006038188934326</v>
+        <v>7.786178350448608</v>
       </c>
       <c r="G17" t="n">
-        <v>8.5278000831604</v>
+        <v>7.66550087928772</v>
       </c>
       <c r="H17" t="n">
-        <v>8.815614461898804</v>
+        <v>8.84235405921936</v>
       </c>
       <c r="I17" t="n">
-        <v>8.946793794631958</v>
+        <v>7.539837121963501</v>
       </c>
       <c r="J17" t="n">
-        <v>9.652926683425903</v>
+        <v>9.802786350250244</v>
       </c>
       <c r="K17" t="n">
-        <v>9.732783555984497</v>
+        <v>7.466034412384033</v>
       </c>
       <c r="L17" t="n">
-        <v>8.899251008033753</v>
+        <v>8.013570141792297</v>
       </c>
     </row>
     <row r="18">
@@ -3070,37 +3070,37 @@
         <v>24</v>
       </c>
       <c r="B18" t="n">
-        <v>9.924225091934204</v>
+        <v>8.510242462158203</v>
       </c>
       <c r="C18" t="n">
-        <v>8.426552534103394</v>
+        <v>8.29382061958313</v>
       </c>
       <c r="D18" t="n">
-        <v>11.37461686134338</v>
+        <v>8.577064275741577</v>
       </c>
       <c r="E18" t="n">
-        <v>10.44601583480835</v>
+        <v>8.698737144470215</v>
       </c>
       <c r="F18" t="n">
-        <v>11.63644337654114</v>
+        <v>8.624935388565063</v>
       </c>
       <c r="G18" t="n">
-        <v>10.97258353233337</v>
+        <v>8.298807621002197</v>
       </c>
       <c r="H18" t="n">
-        <v>10.37855529785156</v>
+        <v>8.055457830429077</v>
       </c>
       <c r="I18" t="n">
-        <v>8.984590530395508</v>
+        <v>8.574071884155273</v>
       </c>
       <c r="J18" t="n">
-        <v>9.210554838180542</v>
+        <v>8.09136176109314</v>
       </c>
       <c r="K18" t="n">
-        <v>9.107313871383667</v>
+        <v>8.488300561904907</v>
       </c>
       <c r="L18" t="n">
-        <v>10.04614517688751</v>
+        <v>8.421279954910279</v>
       </c>
     </row>
     <row r="19">
@@ -3108,37 +3108,37 @@
         <v>25</v>
       </c>
       <c r="B19" t="n">
-        <v>7.190671920776367</v>
+        <v>6.022893905639648</v>
       </c>
       <c r="C19" t="n">
-        <v>7.183714628219604</v>
+        <v>6.402877330780029</v>
       </c>
       <c r="D19" t="n">
-        <v>8.182646989822388</v>
+        <v>6.993297576904297</v>
       </c>
       <c r="E19" t="n">
-        <v>8.778464794158936</v>
+        <v>5.944094657897949</v>
       </c>
       <c r="F19" t="n">
-        <v>6.604152679443359</v>
+        <v>6.836717367172241</v>
       </c>
       <c r="G19" t="n">
-        <v>6.697463989257812</v>
+        <v>7.467031002044678</v>
       </c>
       <c r="H19" t="n">
-        <v>8.645965814590454</v>
+        <v>6.535523176193237</v>
       </c>
       <c r="I19" t="n">
-        <v>8.101864576339722</v>
+        <v>7.406194448471069</v>
       </c>
       <c r="J19" t="n">
-        <v>8.072453737258911</v>
+        <v>6.981330394744873</v>
       </c>
       <c r="K19" t="n">
-        <v>8.736232757568359</v>
+        <v>6.811784267425537</v>
       </c>
       <c r="L19" t="n">
-        <v>7.819363188743591</v>
+        <v>6.740174412727356</v>
       </c>
     </row>
     <row r="20">
@@ -3146,37 +3146,37 @@
         <v>26</v>
       </c>
       <c r="B20" t="n">
-        <v>7.99109935760498</v>
+        <v>7.557788610458374</v>
       </c>
       <c r="C20" t="n">
-        <v>8.31828498840332</v>
+        <v>6.696094036102295</v>
       </c>
       <c r="D20" t="n">
-        <v>8.45461106300354</v>
+        <v>7.507921695709229</v>
       </c>
       <c r="E20" t="n">
-        <v>7.584352970123291</v>
+        <v>7.861975431442261</v>
       </c>
       <c r="F20" t="n">
-        <v>8.154806852340698</v>
+        <v>7.197751760482788</v>
       </c>
       <c r="G20" t="n">
-        <v>9.684772253036499</v>
+        <v>7.810114145278931</v>
       </c>
       <c r="H20" t="n">
-        <v>7.876074552536011</v>
+        <v>7.915831565856934</v>
       </c>
       <c r="I20" t="n">
-        <v>9.062424182891846</v>
+        <v>7.625607967376709</v>
       </c>
       <c r="J20" t="n">
-        <v>8.628547668457031</v>
+        <v>7.284520149230957</v>
       </c>
       <c r="K20" t="n">
-        <v>8.384213924407959</v>
+        <v>8.19208812713623</v>
       </c>
       <c r="L20" t="n">
-        <v>8.413918781280518</v>
+        <v>7.564969348907471</v>
       </c>
     </row>
     <row r="21">
@@ -3184,37 +3184,37 @@
         <v>27</v>
       </c>
       <c r="B21" t="n">
-        <v>8.46349024772644</v>
+        <v>8.61795449256897</v>
       </c>
       <c r="C21" t="n">
-        <v>8.703364610671997</v>
+        <v>6.826743364334106</v>
       </c>
       <c r="D21" t="n">
-        <v>8.34577202796936</v>
+        <v>7.183789491653442</v>
       </c>
       <c r="E21" t="n">
-        <v>9.872310638427734</v>
+        <v>7.289506673812866</v>
       </c>
       <c r="F21" t="n">
-        <v>9.24002742767334</v>
+        <v>9.510566473007202</v>
       </c>
       <c r="G21" t="n">
-        <v>8.434077739715576</v>
+        <v>7.597682237625122</v>
       </c>
       <c r="H21" t="n">
-        <v>9.100821256637573</v>
+        <v>7.275544166564941</v>
       </c>
       <c r="I21" t="n">
-        <v>7.805707216262817</v>
+        <v>8.782513618469238</v>
       </c>
       <c r="J21" t="n">
-        <v>7.535914421081543</v>
+        <v>8.972006797790527</v>
       </c>
       <c r="K21" t="n">
-        <v>9.148700952529907</v>
+        <v>7.68345308303833</v>
       </c>
       <c r="L21" t="n">
-        <v>8.665018653869629</v>
+        <v>7.973976039886475</v>
       </c>
     </row>
     <row r="22">
@@ -3222,37 +3222,37 @@
         <v>28</v>
       </c>
       <c r="B22" t="n">
-        <v>8.120394706726074</v>
+        <v>7.338376522064209</v>
       </c>
       <c r="C22" t="n">
-        <v>7.40473198890686</v>
+        <v>8.747607707977295</v>
       </c>
       <c r="D22" t="n">
-        <v>7.598272562026978</v>
+        <v>6.716039419174194</v>
       </c>
       <c r="E22" t="n">
-        <v>6.909530639648438</v>
+        <v>7.666497707366943</v>
       </c>
       <c r="F22" t="n">
-        <v>9.14071249961853</v>
+        <v>6.644231796264648</v>
       </c>
       <c r="G22" t="n">
-        <v>7.192291736602783</v>
+        <v>7.431127786636353</v>
       </c>
       <c r="H22" t="n">
-        <v>7.276091337203979</v>
+        <v>7.469025373458862</v>
       </c>
       <c r="I22" t="n">
-        <v>8.687921524047852</v>
+        <v>8.088370561599731</v>
       </c>
       <c r="J22" t="n">
-        <v>7.712445497512817</v>
+        <v>8.326732873916626</v>
       </c>
       <c r="K22" t="n">
-        <v>7.419669389724731</v>
+        <v>7.448082685470581</v>
       </c>
       <c r="L22" t="n">
-        <v>7.746206188201905</v>
+        <v>7.587609243392945</v>
       </c>
     </row>
     <row r="23">
@@ -3260,37 +3260,37 @@
         <v>29</v>
       </c>
       <c r="B23" t="n">
-        <v>10.6597957611084</v>
+        <v>8.128263711929321</v>
       </c>
       <c r="C23" t="n">
-        <v>8.796585083007812</v>
+        <v>7.811110734939575</v>
       </c>
       <c r="D23" t="n">
-        <v>9.708260774612427</v>
+        <v>7.624610424041748</v>
       </c>
       <c r="E23" t="n">
-        <v>9.911614418029785</v>
+        <v>9.446507453918457</v>
       </c>
       <c r="F23" t="n">
-        <v>9.878372192382812</v>
+        <v>8.431452989578247</v>
       </c>
       <c r="G23" t="n">
-        <v>10.1755850315094</v>
+        <v>8.306786060333252</v>
       </c>
       <c r="H23" t="n">
-        <v>8.134759426116943</v>
+        <v>9.345009803771973</v>
       </c>
       <c r="I23" t="n">
-        <v>9.468633651733398</v>
+        <v>9.905936717987061</v>
       </c>
       <c r="J23" t="n">
-        <v>9.512733936309814</v>
+        <v>8.522209405899048</v>
       </c>
       <c r="K23" t="n">
-        <v>9.823530197143555</v>
+        <v>8.674631834030151</v>
       </c>
       <c r="L23" t="n">
-        <v>9.606987047195435</v>
+        <v>8.619651913642883</v>
       </c>
     </row>
     <row r="24">
@@ -3298,37 +3298,37 @@
         <v>3</v>
       </c>
       <c r="B24" t="n">
-        <v>8.110404253005981</v>
+        <v>8.475334882736206</v>
       </c>
       <c r="C24" t="n">
-        <v>8.678423643112183</v>
+        <v>7.285516977310181</v>
       </c>
       <c r="D24" t="n">
-        <v>8.537786960601807</v>
+        <v>7.443095207214355</v>
       </c>
       <c r="E24" t="n">
-        <v>7.925862073898315</v>
+        <v>8.00757908821106</v>
       </c>
       <c r="F24" t="n">
-        <v>7.76131010055542</v>
+        <v>8.508246421813965</v>
       </c>
       <c r="G24" t="n">
-        <v>8.605613708496094</v>
+        <v>7.241236448287964</v>
       </c>
       <c r="H24" t="n">
-        <v>7.512009382247925</v>
+        <v>7.059122562408447</v>
       </c>
       <c r="I24" t="n">
-        <v>8.642501354217529</v>
+        <v>7.097021102905273</v>
       </c>
       <c r="J24" t="n">
-        <v>7.700449705123901</v>
+        <v>6.886316537857056</v>
       </c>
       <c r="K24" t="n">
-        <v>7.495983123779297</v>
+        <v>7.151874303817749</v>
       </c>
       <c r="L24" t="n">
-        <v>8.097034430503845</v>
+        <v>7.515534353256226</v>
       </c>
     </row>
     <row r="25">
@@ -3336,37 +3336,37 @@
         <v>30</v>
       </c>
       <c r="B25" t="n">
-        <v>10.70164704322815</v>
+        <v>8.449404001235962</v>
       </c>
       <c r="C25" t="n">
-        <v>8.927308320999146</v>
+        <v>8.70155668258667</v>
       </c>
       <c r="D25" t="n">
-        <v>11.73299670219421</v>
+        <v>8.48829984664917</v>
       </c>
       <c r="E25" t="n">
-        <v>10.81185579299927</v>
+        <v>9.878582239151001</v>
       </c>
       <c r="F25" t="n">
-        <v>9.695787668228149</v>
+        <v>8.304791927337646</v>
       </c>
       <c r="G25" t="n">
-        <v>11.7355432510376</v>
+        <v>9.155515432357788</v>
       </c>
       <c r="H25" t="n">
-        <v>9.319764852523804</v>
+        <v>8.357621669769287</v>
       </c>
       <c r="I25" t="n">
-        <v>8.251551866531372</v>
+        <v>9.926454782485962</v>
       </c>
       <c r="J25" t="n">
-        <v>8.780255079269409</v>
+        <v>8.970012187957764</v>
       </c>
       <c r="K25" t="n">
-        <v>8.642467737197876</v>
+        <v>9.480647325515747</v>
       </c>
       <c r="L25" t="n">
-        <v>9.859917831420898</v>
+        <v>8.9712886095047</v>
       </c>
     </row>
     <row r="26">
@@ -3374,37 +3374,37 @@
         <v>31</v>
       </c>
       <c r="B26" t="n">
-        <v>7.996621131896973</v>
+        <v>8.298807144165039</v>
       </c>
       <c r="C26" t="n">
-        <v>10.1915111541748</v>
+        <v>9.780844926834106</v>
       </c>
       <c r="D26" t="n">
-        <v>8.224294900894165</v>
+        <v>8.206786394119263</v>
       </c>
       <c r="E26" t="n">
-        <v>9.786588907241821</v>
+        <v>8.485116720199585</v>
       </c>
       <c r="F26" t="n">
-        <v>7.763277053833008</v>
+        <v>8.084379911422729</v>
       </c>
       <c r="G26" t="n">
-        <v>8.542302846908569</v>
+        <v>7.600674867630005</v>
       </c>
       <c r="H26" t="n">
-        <v>9.368594169616699</v>
+        <v>8.422475814819336</v>
       </c>
       <c r="I26" t="n">
-        <v>7.996623277664185</v>
+        <v>7.576104164123535</v>
       </c>
       <c r="J26" t="n">
-        <v>8.387112379074097</v>
+        <v>8.234647989273071</v>
       </c>
       <c r="K26" t="n">
-        <v>8.3352370262146</v>
+        <v>8.125771999359131</v>
       </c>
       <c r="L26" t="n">
-        <v>8.659216284751892</v>
+        <v>8.28156099319458</v>
       </c>
     </row>
     <row r="27">
@@ -3412,37 +3412,37 @@
         <v>32</v>
       </c>
       <c r="B27" t="n">
-        <v>9.103273630142212</v>
+        <v>8.613360404968262</v>
       </c>
       <c r="C27" t="n">
-        <v>8.672869443893433</v>
+        <v>8.557116270065308</v>
       </c>
       <c r="D27" t="n">
-        <v>9.145212411880493</v>
+        <v>9.708038806915283</v>
       </c>
       <c r="E27" t="n">
-        <v>8.312317848205566</v>
+        <v>8.727446556091309</v>
       </c>
       <c r="F27" t="n">
-        <v>10.51571011543274</v>
+        <v>8.749201536178589</v>
       </c>
       <c r="G27" t="n">
-        <v>8.761675596237183</v>
+        <v>9.888450622558594</v>
       </c>
       <c r="H27" t="n">
-        <v>8.881340503692627</v>
+        <v>8.446411848068237</v>
       </c>
       <c r="I27" t="n">
-        <v>8.534757852554321</v>
+        <v>8.971009731292725</v>
       </c>
       <c r="J27" t="n">
-        <v>10.14815163612366</v>
+        <v>8.871276140213013</v>
       </c>
       <c r="K27" t="n">
-        <v>8.703235864639282</v>
+        <v>8.495281457901001</v>
       </c>
       <c r="L27" t="n">
-        <v>9.077854490280151</v>
+        <v>8.902759337425232</v>
       </c>
     </row>
     <row r="28">
@@ -3450,37 +3450,37 @@
         <v>33</v>
       </c>
       <c r="B28" t="n">
-        <v>7.267991065979004</v>
+        <v>7.203736066818237</v>
       </c>
       <c r="C28" t="n">
-        <v>8.409575223922729</v>
+        <v>7.350343704223633</v>
       </c>
       <c r="D28" t="n">
-        <v>7.746772766113281</v>
+        <v>6.897916316986084</v>
       </c>
       <c r="E28" t="n">
-        <v>8.902810573577881</v>
+        <v>7.594689846038818</v>
       </c>
       <c r="F28" t="n">
-        <v>7.644513368606567</v>
+        <v>7.336320161819458</v>
       </c>
       <c r="G28" t="n">
-        <v>9.134226322174072</v>
+        <v>7.401655673980713</v>
       </c>
       <c r="H28" t="n">
-        <v>8.969178676605225</v>
+        <v>8.141841888427734</v>
       </c>
       <c r="I28" t="n">
-        <v>9.237447500228882</v>
+        <v>7.360456466674805</v>
       </c>
       <c r="J28" t="n">
-        <v>8.859405994415283</v>
+        <v>7.141426563262939</v>
       </c>
       <c r="K28" t="n">
-        <v>8.785590171813965</v>
+        <v>6.96138334274292</v>
       </c>
       <c r="L28" t="n">
-        <v>8.495751166343689</v>
+        <v>7.338977003097535</v>
       </c>
     </row>
     <row r="29">
@@ -3488,37 +3488,37 @@
         <v>34</v>
       </c>
       <c r="B29" t="n">
-        <v>7.841006517410278</v>
+        <v>7.242632150650024</v>
       </c>
       <c r="C29" t="n">
-        <v>7.109370946884155</v>
+        <v>7.18503999710083</v>
       </c>
       <c r="D29" t="n">
-        <v>9.471879482269287</v>
+        <v>9.197403192520142</v>
       </c>
       <c r="E29" t="n">
-        <v>10.68134593963623</v>
+        <v>7.011250019073486</v>
       </c>
       <c r="F29" t="n">
-        <v>8.623062372207642</v>
+        <v>8.049832582473755</v>
       </c>
       <c r="G29" t="n">
-        <v>9.370593309402466</v>
+        <v>7.031197309494019</v>
       </c>
       <c r="H29" t="n">
-        <v>7.318845510482788</v>
+        <v>6.862647294998169</v>
       </c>
       <c r="I29" t="n">
-        <v>8.264449119567871</v>
+        <v>7.625607967376709</v>
       </c>
       <c r="J29" t="n">
-        <v>7.272509813308716</v>
+        <v>7.552802085876465</v>
       </c>
       <c r="K29" t="n">
-        <v>8.569174289703369</v>
+        <v>8.07261061668396</v>
       </c>
       <c r="L29" t="n">
-        <v>8.45222373008728</v>
+        <v>7.583102321624756</v>
       </c>
     </row>
     <row r="30">
@@ -3526,37 +3526,37 @@
         <v>35</v>
       </c>
       <c r="B30" t="n">
-        <v>8.239287853240967</v>
+        <v>6.858103275299072</v>
       </c>
       <c r="C30" t="n">
-        <v>7.183954477310181</v>
+        <v>7.041290283203125</v>
       </c>
       <c r="D30" t="n">
-        <v>8.925797700881958</v>
+        <v>8.106322050094604</v>
       </c>
       <c r="E30" t="n">
-        <v>8.151743650436401</v>
+        <v>7.147885799407959</v>
       </c>
       <c r="F30" t="n">
-        <v>8.850993633270264</v>
+        <v>7.261581420898438</v>
       </c>
       <c r="G30" t="n">
-        <v>7.535315990447998</v>
+        <v>7.088044881820679</v>
       </c>
       <c r="H30" t="n">
-        <v>7.463989496231079</v>
+        <v>8.25991153717041</v>
       </c>
       <c r="I30" t="n">
-        <v>8.960187911987305</v>
+        <v>7.761244773864746</v>
       </c>
       <c r="J30" t="n">
-        <v>7.128348588943481</v>
+        <v>8.244952440261841</v>
       </c>
       <c r="K30" t="n">
-        <v>9.714765071868896</v>
+        <v>6.849681854248047</v>
       </c>
       <c r="L30" t="n">
-        <v>8.215438437461852</v>
+        <v>7.461901831626892</v>
       </c>
     </row>
     <row r="31">
@@ -3564,37 +3564,37 @@
         <v>36</v>
       </c>
       <c r="B31" t="n">
-        <v>8.731242179870605</v>
+        <v>8.529641389846802</v>
       </c>
       <c r="C31" t="n">
-        <v>7.290932178497314</v>
+        <v>8.372044563293457</v>
       </c>
       <c r="D31" t="n">
-        <v>7.348775148391724</v>
+        <v>8.748973369598389</v>
       </c>
       <c r="E31" t="n">
-        <v>8.620028495788574</v>
+        <v>7.084506273269653</v>
       </c>
       <c r="F31" t="n">
-        <v>9.830972194671631</v>
+        <v>7.667495250701904</v>
       </c>
       <c r="G31" t="n">
-        <v>8.947267532348633</v>
+        <v>7.407191514968872</v>
       </c>
       <c r="H31" t="n">
-        <v>8.053471565246582</v>
+        <v>7.496951580047607</v>
       </c>
       <c r="I31" t="n">
-        <v>7.875968933105469</v>
+        <v>7.422152280807495</v>
       </c>
       <c r="J31" t="n">
-        <v>7.396181106567383</v>
+        <v>8.89321756362915</v>
       </c>
       <c r="K31" t="n">
-        <v>9.243446111679077</v>
+        <v>7.07807183265686</v>
       </c>
       <c r="L31" t="n">
-        <v>8.333828544616699</v>
+        <v>7.870024561882019</v>
       </c>
     </row>
     <row r="32">
@@ -3602,37 +3602,37 @@
         <v>37</v>
       </c>
       <c r="B32" t="n">
-        <v>8.196628570556641</v>
+        <v>8.188103199005127</v>
       </c>
       <c r="C32" t="n">
-        <v>8.719305992126465</v>
+        <v>9.043814420700073</v>
       </c>
       <c r="D32" t="n">
-        <v>8.332786798477173</v>
+        <v>10.77518486976624</v>
       </c>
       <c r="E32" t="n">
-        <v>9.025038003921509</v>
+        <v>10.0511212348938</v>
       </c>
       <c r="F32" t="n">
-        <v>8.353474378585815</v>
+        <v>8.757728338241577</v>
       </c>
       <c r="G32" t="n">
-        <v>9.459372282028198</v>
+        <v>9.932787179946899</v>
       </c>
       <c r="H32" t="n">
-        <v>9.945165395736694</v>
+        <v>10.47299337387085</v>
       </c>
       <c r="I32" t="n">
-        <v>11.38500475883484</v>
+        <v>9.262031316757202</v>
       </c>
       <c r="J32" t="n">
-        <v>8.939753293991089</v>
+        <v>8.22400689125061</v>
       </c>
       <c r="K32" t="n">
-        <v>8.886856317520142</v>
+        <v>9.294146060943604</v>
       </c>
       <c r="L32" t="n">
-        <v>9.124338579177856</v>
+        <v>9.400191688537598</v>
       </c>
     </row>
     <row r="33">
@@ -3640,37 +3640,37 @@
         <v>38</v>
       </c>
       <c r="B33" t="n">
-        <v>7.817086458206177</v>
+        <v>8.292823076248169</v>
       </c>
       <c r="C33" t="n">
-        <v>7.634548187255859</v>
+        <v>8.210044622421265</v>
       </c>
       <c r="D33" t="n">
-        <v>7.768203735351562</v>
+        <v>7.803133010864258</v>
       </c>
       <c r="E33" t="n">
-        <v>8.057475328445435</v>
+        <v>7.633765697479248</v>
       </c>
       <c r="F33" t="n">
-        <v>7.848052263259888</v>
+        <v>7.343329191207886</v>
       </c>
       <c r="G33" t="n">
-        <v>8.710357427597046</v>
+        <v>11.64392876625061</v>
       </c>
       <c r="H33" t="n">
-        <v>7.921114206314087</v>
+        <v>9.698066234588623</v>
       </c>
       <c r="I33" t="n">
-        <v>7.715825319290161</v>
+        <v>9.408174514770508</v>
       </c>
       <c r="J33" t="n">
-        <v>7.758232355117798</v>
+        <v>9.346914291381836</v>
       </c>
       <c r="K33" t="n">
-        <v>7.608611583709717</v>
+        <v>8.610380411148071</v>
       </c>
       <c r="L33" t="n">
-        <v>7.883950686454773</v>
+        <v>8.799055981636048</v>
       </c>
     </row>
     <row r="34">
@@ -3678,37 +3678,37 @@
         <v>39</v>
       </c>
       <c r="B34" t="n">
-        <v>8.719273567199707</v>
+        <v>9.630258321762085</v>
       </c>
       <c r="C34" t="n">
-        <v>9.486806631088257</v>
+        <v>8.771445035934448</v>
       </c>
       <c r="D34" t="n">
-        <v>8.148244142532349</v>
+        <v>8.783367872238159</v>
       </c>
       <c r="E34" t="n">
-        <v>9.428983926773071</v>
+        <v>8.456145763397217</v>
       </c>
       <c r="F34" t="n">
-        <v>8.301333427429199</v>
+        <v>8.089727401733398</v>
       </c>
       <c r="G34" t="n">
-        <v>7.983137607574463</v>
+        <v>9.515360593795776</v>
       </c>
       <c r="H34" t="n">
-        <v>9.040992975234985</v>
+        <v>8.591204643249512</v>
       </c>
       <c r="I34" t="n">
-        <v>8.589118242263794</v>
+        <v>8.127663373947144</v>
       </c>
       <c r="J34" t="n">
-        <v>8.085932016372681</v>
+        <v>9.412801265716553</v>
       </c>
       <c r="K34" t="n">
-        <v>7.969234466552734</v>
+        <v>7.844641923904419</v>
       </c>
       <c r="L34" t="n">
-        <v>8.575305700302124</v>
+        <v>8.72226161956787</v>
       </c>
     </row>
     <row r="35">
@@ -3716,37 +3716,37 @@
         <v>4</v>
       </c>
       <c r="B35" t="n">
-        <v>8.655964851379395</v>
+        <v>8.276658058166504</v>
       </c>
       <c r="C35" t="n">
-        <v>8.472453594207764</v>
+        <v>7.681353092193604</v>
       </c>
       <c r="D35" t="n">
-        <v>10.15313696861267</v>
+        <v>7.634446859359741</v>
       </c>
       <c r="E35" t="n">
-        <v>7.804119348526001</v>
+        <v>8.236294746398926</v>
       </c>
       <c r="F35" t="n">
-        <v>8.867411136627197</v>
+        <v>7.674414873123169</v>
       </c>
       <c r="G35" t="n">
-        <v>9.3447105884552</v>
+        <v>8.324340581893921</v>
       </c>
       <c r="H35" t="n">
-        <v>9.001075744628906</v>
+        <v>9.724870920181274</v>
       </c>
       <c r="I35" t="n">
-        <v>8.660461902618408</v>
+        <v>7.600133657455444</v>
       </c>
       <c r="J35" t="n">
-        <v>7.961198568344116</v>
+        <v>7.923364400863647</v>
       </c>
       <c r="K35" t="n">
-        <v>8.937031507492065</v>
+        <v>7.780223369598389</v>
       </c>
       <c r="L35" t="n">
-        <v>8.785756421089172</v>
+        <v>8.085610055923462</v>
       </c>
     </row>
     <row r="36">
@@ -3754,37 +3754,37 @@
         <v>40</v>
       </c>
       <c r="B36" t="n">
-        <v>10.83043527603149</v>
+        <v>8.880042314529419</v>
       </c>
       <c r="C36" t="n">
-        <v>8.594110250473022</v>
+        <v>7.950011253356934</v>
       </c>
       <c r="D36" t="n">
-        <v>7.810100317001343</v>
+        <v>7.696947813034058</v>
       </c>
       <c r="E36" t="n">
-        <v>9.59457802772522</v>
+        <v>9.010082244873047</v>
       </c>
       <c r="F36" t="n">
-        <v>10.29475593566895</v>
+        <v>8.406665802001953</v>
       </c>
       <c r="G36" t="n">
-        <v>8.332751750946045</v>
+        <v>7.86260986328125</v>
       </c>
       <c r="H36" t="n">
-        <v>7.807641744613647</v>
+        <v>7.65434193611145</v>
       </c>
       <c r="I36" t="n">
-        <v>7.403711318969727</v>
+        <v>7.919575929641724</v>
       </c>
       <c r="J36" t="n">
-        <v>8.914758682250977</v>
+        <v>7.70896315574646</v>
       </c>
       <c r="K36" t="n">
-        <v>10.30923366546631</v>
+        <v>8.449757814407349</v>
       </c>
       <c r="L36" t="n">
-        <v>8.989207696914672</v>
+        <v>8.153899812698365</v>
       </c>
     </row>
     <row r="37">
@@ -3792,37 +3792,37 @@
         <v>41</v>
       </c>
       <c r="B37" t="n">
-        <v>8.189017057418823</v>
+        <v>7.180360794067383</v>
       </c>
       <c r="C37" t="n">
-        <v>8.181725978851318</v>
+        <v>7.588114261627197</v>
       </c>
       <c r="D37" t="n">
-        <v>7.41870379447937</v>
+        <v>7.114965915679932</v>
       </c>
       <c r="E37" t="n">
-        <v>8.420086145401001</v>
+        <v>7.779851198196411</v>
       </c>
       <c r="F37" t="n">
-        <v>7.313508272171021</v>
+        <v>6.595262765884399</v>
       </c>
       <c r="G37" t="n">
-        <v>7.91790509223938</v>
+        <v>7.348528623580933</v>
       </c>
       <c r="H37" t="n">
-        <v>7.61019492149353</v>
+        <v>7.702772617340088</v>
       </c>
       <c r="I37" t="n">
-        <v>8.138381719589233</v>
+        <v>6.81913948059082</v>
       </c>
       <c r="J37" t="n">
-        <v>7.249135494232178</v>
+        <v>7.226784944534302</v>
       </c>
       <c r="K37" t="n">
-        <v>7.777764797210693</v>
+        <v>7.082716941833496</v>
       </c>
       <c r="L37" t="n">
-        <v>7.821642327308655</v>
+        <v>7.243849754333496</v>
       </c>
     </row>
     <row r="38">
@@ -3830,37 +3830,37 @@
         <v>42</v>
       </c>
       <c r="B38" t="n">
-        <v>6.780330657958984</v>
+        <v>7.607721567153931</v>
       </c>
       <c r="C38" t="n">
-        <v>7.592225313186646</v>
+        <v>7.430045127868652</v>
       </c>
       <c r="D38" t="n">
-        <v>7.541872978210449</v>
+        <v>6.944466352462769</v>
       </c>
       <c r="E38" t="n">
-        <v>7.617196798324585</v>
+        <v>7.241742610931396</v>
       </c>
       <c r="F38" t="n">
-        <v>7.502976179122925</v>
+        <v>7.569323062896729</v>
       </c>
       <c r="G38" t="n">
-        <v>7.736408233642578</v>
+        <v>7.481713533401489</v>
       </c>
       <c r="H38" t="n">
-        <v>8.251527070999146</v>
+        <v>7.369225263595581</v>
       </c>
       <c r="I38" t="n">
-        <v>8.013129949569702</v>
+        <v>7.500317811965942</v>
       </c>
       <c r="J38" t="n">
-        <v>8.572109460830688</v>
+        <v>7.698054075241089</v>
       </c>
       <c r="K38" t="n">
-        <v>7.746757507324219</v>
+        <v>7.287703275680542</v>
       </c>
       <c r="L38" t="n">
-        <v>7.735453414916992</v>
+        <v>7.413031268119812</v>
       </c>
     </row>
     <row r="39">
@@ -3868,37 +3868,37 @@
         <v>43</v>
       </c>
       <c r="B39" t="n">
-        <v>8.419554471969604</v>
+        <v>7.539918184280396</v>
       </c>
       <c r="C39" t="n">
-        <v>9.264877796173096</v>
+        <v>7.993911743164062</v>
       </c>
       <c r="D39" t="n">
-        <v>8.110335826873779</v>
+        <v>8.576172590255737</v>
       </c>
       <c r="E39" t="n">
-        <v>8.26842737197876</v>
+        <v>7.975770473480225</v>
       </c>
       <c r="F39" t="n">
-        <v>8.265928506851196</v>
+        <v>8.041815757751465</v>
       </c>
       <c r="G39" t="n">
-        <v>7.711850881576538</v>
+        <v>9.166245460510254</v>
       </c>
       <c r="H39" t="n">
-        <v>8.810544967651367</v>
+        <v>9.50745677947998</v>
       </c>
       <c r="I39" t="n">
-        <v>9.395653247833252</v>
+        <v>7.983246088027954</v>
       </c>
       <c r="J39" t="n">
-        <v>8.551690816879272</v>
+        <v>8.975838184356689</v>
       </c>
       <c r="K39" t="n">
-        <v>8.928761720657349</v>
+        <v>7.872861623764038</v>
       </c>
       <c r="L39" t="n">
-        <v>8.572762560844421</v>
+        <v>8.36332368850708</v>
       </c>
     </row>
     <row r="40">
@@ -3906,37 +3906,37 @@
         <v>44</v>
       </c>
       <c r="B40" t="n">
-        <v>9.42399263381958</v>
+        <v>7.649411201477051</v>
       </c>
       <c r="C40" t="n">
-        <v>7.621552467346191</v>
+        <v>7.035219430923462</v>
       </c>
       <c r="D40" t="n">
-        <v>7.988158464431763</v>
+        <v>7.684327363967896</v>
       </c>
       <c r="E40" t="n">
-        <v>8.358691453933716</v>
+        <v>7.584991693496704</v>
       </c>
       <c r="F40" t="n">
-        <v>7.546256542205811</v>
+        <v>7.216157674789429</v>
       </c>
       <c r="G40" t="n">
-        <v>9.508289813995361</v>
+        <v>7.136238813400269</v>
       </c>
       <c r="H40" t="n">
-        <v>8.573664665222168</v>
+        <v>8.044743299484253</v>
       </c>
       <c r="I40" t="n">
-        <v>7.248079299926758</v>
+        <v>7.489768981933594</v>
       </c>
       <c r="J40" t="n">
-        <v>6.678990364074707</v>
+        <v>8.144711256027222</v>
       </c>
       <c r="K40" t="n">
-        <v>7.606622219085693</v>
+        <v>7.088753461837769</v>
       </c>
       <c r="L40" t="n">
-        <v>8.055429792404174</v>
+        <v>7.507432317733764</v>
       </c>
     </row>
     <row r="41">
@@ -3944,37 +3944,37 @@
         <v>45</v>
       </c>
       <c r="B41" t="n">
-        <v>10.00354957580566</v>
+        <v>7.055048704147339</v>
       </c>
       <c r="C41" t="n">
-        <v>9.397182703018188</v>
+        <v>7.693621635437012</v>
       </c>
       <c r="D41" t="n">
-        <v>7.15191125869751</v>
+        <v>6.819525480270386</v>
       </c>
       <c r="E41" t="n">
-        <v>7.557373762130737</v>
+        <v>7.791278600692749</v>
       </c>
       <c r="F41" t="n">
-        <v>9.39804220199585</v>
+        <v>7.496066331863403</v>
       </c>
       <c r="G41" t="n">
-        <v>10.04938983917236</v>
+        <v>6.667470455169678</v>
       </c>
       <c r="H41" t="n">
-        <v>7.808689594268799</v>
+        <v>6.778546094894409</v>
       </c>
       <c r="I41" t="n">
-        <v>7.38228178024292</v>
+        <v>6.550864458084106</v>
       </c>
       <c r="J41" t="n">
-        <v>7.966283321380615</v>
+        <v>8.103895902633667</v>
       </c>
       <c r="K41" t="n">
-        <v>7.737364768981934</v>
+        <v>7.494782209396362</v>
       </c>
       <c r="L41" t="n">
-        <v>8.445206880569458</v>
+        <v>7.245109987258911</v>
       </c>
     </row>
     <row r="42">
@@ -3982,37 +3982,37 @@
         <v>46</v>
       </c>
       <c r="B42" t="n">
-        <v>8.082468509674072</v>
+        <v>7.640483617782593</v>
       </c>
       <c r="C42" t="n">
-        <v>10.95497989654541</v>
+        <v>8.36016321182251</v>
       </c>
       <c r="D42" t="n">
-        <v>8.426076650619507</v>
+        <v>8.020934343338013</v>
       </c>
       <c r="E42" t="n">
-        <v>8.725831031799316</v>
+        <v>7.51415491104126</v>
       </c>
       <c r="F42" t="n">
-        <v>8.29689621925354</v>
+        <v>8.416704416275024</v>
       </c>
       <c r="G42" t="n">
-        <v>10.07671976089478</v>
+        <v>7.548835039138794</v>
       </c>
       <c r="H42" t="n">
-        <v>7.532751798629761</v>
+        <v>8.570304393768311</v>
       </c>
       <c r="I42" t="n">
-        <v>8.524765014648438</v>
+        <v>7.426330804824829</v>
       </c>
       <c r="J42" t="n">
-        <v>9.135266780853271</v>
+        <v>14.83222794532776</v>
       </c>
       <c r="K42" t="n">
-        <v>8.472394704818726</v>
+        <v>9.950117111206055</v>
       </c>
       <c r="L42" t="n">
-        <v>8.822815036773681</v>
+        <v>8.828025579452515</v>
       </c>
     </row>
     <row r="43">
@@ -4020,37 +4020,37 @@
         <v>47</v>
       </c>
       <c r="B43" t="n">
-        <v>8.072472333908081</v>
+        <v>7.976166248321533</v>
       </c>
       <c r="C43" t="n">
-        <v>10.28632998466492</v>
+        <v>8.122824430465698</v>
       </c>
       <c r="D43" t="n">
-        <v>9.00506854057312</v>
+        <v>8.077531099319458</v>
       </c>
       <c r="E43" t="n">
-        <v>9.107518196105957</v>
+        <v>7.231345653533936</v>
       </c>
       <c r="F43" t="n">
-        <v>7.269081115722656</v>
+        <v>7.437448024749756</v>
       </c>
       <c r="G43" t="n">
-        <v>7.781794786453247</v>
+        <v>7.787821769714355</v>
       </c>
       <c r="H43" t="n">
-        <v>8.335786581039429</v>
+        <v>7.030293941497803</v>
       </c>
       <c r="I43" t="n">
-        <v>8.040055990219116</v>
+        <v>7.491599559783936</v>
       </c>
       <c r="J43" t="n">
-        <v>7.373790502548218</v>
+        <v>7.931975841522217</v>
       </c>
       <c r="K43" t="n">
-        <v>7.771264553070068</v>
+        <v>9.137039184570312</v>
       </c>
       <c r="L43" t="n">
-        <v>8.304316258430481</v>
+        <v>7.822404575347901</v>
       </c>
     </row>
     <row r="44">
@@ -4058,37 +4058,37 @@
         <v>48</v>
       </c>
       <c r="B44" t="n">
-        <v>6.800279855728149</v>
+        <v>7.097652673721313</v>
       </c>
       <c r="C44" t="n">
-        <v>7.967708587646484</v>
+        <v>6.757341623306274</v>
       </c>
       <c r="D44" t="n">
-        <v>6.538877964019775</v>
+        <v>7.827558279037476</v>
       </c>
       <c r="E44" t="n">
-        <v>7.136371612548828</v>
+        <v>6.757842063903809</v>
       </c>
       <c r="F44" t="n">
-        <v>8.151818513870239</v>
+        <v>6.988608360290527</v>
       </c>
       <c r="G44" t="n">
-        <v>7.359745025634766</v>
+        <v>6.595392227172852</v>
       </c>
       <c r="H44" t="n">
-        <v>8.534798622131348</v>
+        <v>8.549568891525269</v>
       </c>
       <c r="I44" t="n">
-        <v>9.264889478683472</v>
+        <v>8.226482391357422</v>
       </c>
       <c r="J44" t="n">
-        <v>7.857966423034668</v>
+        <v>6.648772716522217</v>
       </c>
       <c r="K44" t="n">
-        <v>6.494975328445435</v>
+        <v>6.288191080093384</v>
       </c>
       <c r="L44" t="n">
-        <v>7.610743141174316</v>
+        <v>7.173741030693054</v>
       </c>
     </row>
     <row r="45">
@@ -4096,37 +4096,37 @@
         <v>49</v>
       </c>
       <c r="B45" t="n">
-        <v>8.775141716003418</v>
+        <v>9.321865797042847</v>
       </c>
       <c r="C45" t="n">
-        <v>9.093806982040405</v>
+        <v>9.12180233001709</v>
       </c>
       <c r="D45" t="n">
-        <v>9.557664632797241</v>
+        <v>8.891484975814819</v>
       </c>
       <c r="E45" t="n">
-        <v>7.922298908233643</v>
+        <v>8.257653713226318</v>
       </c>
       <c r="F45" t="n">
-        <v>8.253568410873413</v>
+        <v>9.201034784317017</v>
       </c>
       <c r="G45" t="n">
-        <v>9.090359687805176</v>
+        <v>9.116987228393555</v>
       </c>
       <c r="H45" t="n">
-        <v>8.549731731414795</v>
+        <v>9.689127206802368</v>
       </c>
       <c r="I45" t="n">
-        <v>9.183600902557373</v>
+        <v>10.24901652336121</v>
       </c>
       <c r="J45" t="n">
-        <v>8.535746097564697</v>
+        <v>9.969099521636963</v>
       </c>
       <c r="K45" t="n">
-        <v>9.753722429275513</v>
+        <v>10.46747136116028</v>
       </c>
       <c r="L45" t="n">
-        <v>8.871564149856567</v>
+        <v>9.428554344177247</v>
       </c>
     </row>
     <row r="46">
@@ -4134,37 +4134,37 @@
         <v>5</v>
       </c>
       <c r="B46" t="n">
-        <v>7.657077312469482</v>
+        <v>7.227753400802612</v>
       </c>
       <c r="C46" t="n">
-        <v>8.559729337692261</v>
+        <v>7.495879173278809</v>
       </c>
       <c r="D46" t="n">
-        <v>7.480065822601318</v>
+        <v>6.702198505401611</v>
       </c>
       <c r="E46" t="n">
-        <v>6.880077123641968</v>
+        <v>7.618460416793823</v>
       </c>
       <c r="F46" t="n">
-        <v>6.914511442184448</v>
+        <v>8.676470041275024</v>
       </c>
       <c r="G46" t="n">
-        <v>7.126944065093994</v>
+        <v>8.983370065689087</v>
       </c>
       <c r="H46" t="n">
-        <v>8.580697059631348</v>
+        <v>7.560222625732422</v>
       </c>
       <c r="I46" t="n">
-        <v>8.769680738449097</v>
+        <v>8.425729513168335</v>
       </c>
       <c r="J46" t="n">
-        <v>7.047204971313477</v>
+        <v>7.638043880462646</v>
       </c>
       <c r="K46" t="n">
-        <v>7.106025218963623</v>
+        <v>8.580128908157349</v>
       </c>
       <c r="L46" t="n">
-        <v>7.612201309204101</v>
+        <v>7.890825653076172</v>
       </c>
     </row>
     <row r="47">
@@ -4172,37 +4172,37 @@
         <v>50</v>
       </c>
       <c r="B47" t="n">
-        <v>8.582171678543091</v>
+        <v>8.308228015899658</v>
       </c>
       <c r="C47" t="n">
-        <v>12.03815889358521</v>
+        <v>8.636553764343262</v>
       </c>
       <c r="D47" t="n">
-        <v>8.184248208999634</v>
+        <v>8.659172773361206</v>
       </c>
       <c r="E47" t="n">
-        <v>10.78494548797607</v>
+        <v>9.919217586517334</v>
       </c>
       <c r="F47" t="n">
-        <v>9.513781309127808</v>
+        <v>9.318072319030762</v>
       </c>
       <c r="G47" t="n">
-        <v>8.589151382446289</v>
+        <v>8.085698843002319</v>
       </c>
       <c r="H47" t="n">
-        <v>9.249436378479004</v>
+        <v>8.284759283065796</v>
       </c>
       <c r="I47" t="n">
-        <v>9.773078203201294</v>
+        <v>9.201658487319946</v>
       </c>
       <c r="J47" t="n">
-        <v>9.021533727645874</v>
+        <v>8.245194435119629</v>
       </c>
       <c r="K47" t="n">
-        <v>8.307895421981812</v>
+        <v>8.299462080001831</v>
       </c>
       <c r="L47" t="n">
-        <v>9.404440069198609</v>
+        <v>8.695801758766175</v>
       </c>
     </row>
     <row r="48">
@@ -4210,37 +4210,37 @@
         <v>6</v>
       </c>
       <c r="B48" t="n">
-        <v>7.548839330673218</v>
+        <v>7.163079261779785</v>
       </c>
       <c r="C48" t="n">
-        <v>6.432770013809204</v>
+        <v>6.489652633666992</v>
       </c>
       <c r="D48" t="n">
-        <v>8.161286354064941</v>
+        <v>6.941042423248291</v>
       </c>
       <c r="E48" t="n">
-        <v>6.310077428817749</v>
+        <v>7.163412094116211</v>
       </c>
       <c r="F48" t="n">
-        <v>8.028120040893555</v>
+        <v>6.871762990951538</v>
       </c>
       <c r="G48" t="n">
-        <v>8.93830943107605</v>
+        <v>6.657304048538208</v>
       </c>
       <c r="H48" t="n">
-        <v>6.808294773101807</v>
+        <v>6.479028463363647</v>
       </c>
       <c r="I48" t="n">
-        <v>8.564728021621704</v>
+        <v>6.783011436462402</v>
       </c>
       <c r="J48" t="n">
-        <v>7.162881374359131</v>
+        <v>6.816365957260132</v>
       </c>
       <c r="K48" t="n">
-        <v>7.0740966796875</v>
+        <v>7.166757583618164</v>
       </c>
       <c r="L48" t="n">
-        <v>7.502940344810486</v>
+        <v>6.853141689300537</v>
       </c>
     </row>
     <row r="49">
@@ -4248,37 +4248,37 @@
         <v>7</v>
       </c>
       <c r="B49" t="n">
-        <v>8.198669910430908</v>
+        <v>7.352431058883667</v>
       </c>
       <c r="C49" t="n">
-        <v>7.711452484130859</v>
+        <v>8.10195255279541</v>
       </c>
       <c r="D49" t="n">
-        <v>8.464998722076416</v>
+        <v>7.783468723297119</v>
       </c>
       <c r="E49" t="n">
-        <v>7.25464916229248</v>
+        <v>7.065430402755737</v>
       </c>
       <c r="F49" t="n">
-        <v>8.311372756958008</v>
+        <v>7.641607999801636</v>
       </c>
       <c r="G49" t="n">
-        <v>7.939734220504761</v>
+        <v>7.134142637252808</v>
       </c>
       <c r="H49" t="n">
-        <v>7.996103525161743</v>
+        <v>7.61673641204834</v>
       </c>
       <c r="I49" t="n">
-        <v>8.613044738769531</v>
+        <v>7.989614486694336</v>
       </c>
       <c r="J49" t="n">
-        <v>8.559178113937378</v>
+        <v>8.513979434967041</v>
       </c>
       <c r="K49" t="n">
-        <v>8.575621366500854</v>
+        <v>6.908687114715576</v>
       </c>
       <c r="L49" t="n">
-        <v>8.162482500076294</v>
+        <v>7.610805082321167</v>
       </c>
     </row>
     <row r="50">
@@ -4286,37 +4286,37 @@
         <v>8</v>
       </c>
       <c r="B50" t="n">
-        <v>7.772686958312988</v>
+        <v>8.035520315170288</v>
       </c>
       <c r="C50" t="n">
-        <v>10.58904242515564</v>
+        <v>8.638559103012085</v>
       </c>
       <c r="D50" t="n">
-        <v>7.746758699417114</v>
+        <v>8.573259353637695</v>
       </c>
       <c r="E50" t="n">
-        <v>8.040501832962036</v>
+        <v>8.240998268127441</v>
       </c>
       <c r="F50" t="n">
-        <v>9.157662630081177</v>
+        <v>8.559258222579956</v>
       </c>
       <c r="G50" t="n">
-        <v>8.243021965026855</v>
+        <v>7.694617748260498</v>
       </c>
       <c r="H50" t="n">
-        <v>8.028549909591675</v>
+        <v>8.838364839553833</v>
       </c>
       <c r="I50" t="n">
-        <v>8.686341762542725</v>
+        <v>7.291500806808472</v>
       </c>
       <c r="J50" t="n">
-        <v>7.872994899749756</v>
+        <v>8.932113647460938</v>
       </c>
       <c r="K50" t="n">
-        <v>10.4224259853363</v>
+        <v>8.485308647155762</v>
       </c>
       <c r="L50" t="n">
-        <v>8.655998706817627</v>
+        <v>8.328950095176697</v>
       </c>
     </row>
     <row r="51">
@@ -4324,37 +4324,37 @@
         <v>9</v>
       </c>
       <c r="B51" t="n">
-        <v>7.945758819580078</v>
+        <v>8.374345541000366</v>
       </c>
       <c r="C51" t="n">
-        <v>6.862500667572021</v>
+        <v>7.134920120239258</v>
       </c>
       <c r="D51" t="n">
-        <v>8.174190044403076</v>
+        <v>7.165836811065674</v>
       </c>
       <c r="E51" t="n">
-        <v>7.884955406188965</v>
+        <v>6.450748920440674</v>
       </c>
       <c r="F51" t="n">
-        <v>7.596686840057373</v>
+        <v>6.773883819580078</v>
       </c>
       <c r="G51" t="n">
-        <v>8.643011093139648</v>
+        <v>7.549716234207153</v>
       </c>
       <c r="H51" t="n">
-        <v>8.44386625289917</v>
+        <v>6.78286075592041</v>
       </c>
       <c r="I51" t="n">
-        <v>7.922889471054077</v>
+        <v>6.744962215423584</v>
       </c>
       <c r="J51" t="n">
-        <v>6.631753921508789</v>
+        <v>7.663506507873535</v>
       </c>
       <c r="K51" t="n">
-        <v>8.242553234100342</v>
+        <v>7.281124114990234</v>
       </c>
       <c r="L51" t="n">
-        <v>7.834816575050354</v>
+        <v>7.192190504074096</v>
       </c>
     </row>
     <row r="52">
@@ -4364,37 +4364,37 @@
         </is>
       </c>
       <c r="B52" t="n">
-        <v>8.527208819389344</v>
+        <v>8.075302114486695</v>
       </c>
       <c r="C52" t="n">
-        <v>8.496058363914489</v>
+        <v>7.965503005981446</v>
       </c>
       <c r="D52" t="n">
-        <v>8.371908397674561</v>
+        <v>7.96895339012146</v>
       </c>
       <c r="E52" t="n">
-        <v>8.674661808013916</v>
+        <v>7.896723732948304</v>
       </c>
       <c r="F52" t="n">
-        <v>8.548358292579652</v>
+        <v>7.903992528915405</v>
       </c>
       <c r="G52" t="n">
-        <v>8.557457613945008</v>
+        <v>7.985011558532715</v>
       </c>
       <c r="H52" t="n">
-        <v>8.404134621620178</v>
+        <v>8.078013401031495</v>
       </c>
       <c r="I52" t="n">
-        <v>8.604748163223267</v>
+        <v>7.988316836357117</v>
       </c>
       <c r="J52" t="n">
-        <v>8.402979907989502</v>
+        <v>8.217279958724976</v>
       </c>
       <c r="K52" t="n">
-        <v>8.54628357410431</v>
+        <v>8.091495075225829</v>
       </c>
       <c r="L52" t="n">
-        <v>8.513379956245423</v>
+        <v>8.017059160232543</v>
       </c>
     </row>
   </sheetData>
